--- a/ميديكسا.xlsx
+++ b/ميديكسا.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Pharmacy_Operations\Insurance_Accounts\Insurance_Claims\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2B2FF5FC-7D59-442D-85AB-939F1B519694}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4C66B5C8-DE18-4577-A983-18DA1B6DA8A9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -392,7 +392,188 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="14">
+  <dxfs count="27">
+    <dxf>
+      <numFmt numFmtId="19" formatCode="dd/mm/yyyy"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="_-* #,##0.000\ _د_._ا_._‏_-;\-* #,##0.000\ _د_._ا_._‏_-;_-* &quot;-&quot;???\ _د_._ا_._‏_-;_-@_-"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="_-* #,##0.000\ _د_._ا_._‏_-;\-* #,##0.000\ _د_._ا_._‏_-;_-* &quot;-&quot;???\ _د_._ا_._‏_-;_-@_-"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="_-* #,##0.000\ _د_._ا_._‏_-;\-* #,##0.000\ _د_._ا_._‏_-;_-* &quot;-&quot;???\ _د_._ا_._‏_-;_-@_-"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color indexed="8"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="164" formatCode="_-* #,##0.000\ _د_._ا_._‏_-;\-* #,##0.000\ _د_._ا_._‏_-;_-* &quot;-&quot;???\ _د_._ا_._‏_-;_-@_-"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color indexed="8"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="164" formatCode="_-* #,##0.000\ _د_._ا_._‏_-;\-* #,##0.000\ _د_._ا_._‏_-;_-* &quot;-&quot;???\ _د_._ا_._‏_-;_-@_-"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color indexed="8"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="164" formatCode="_-* #,##0.000\ _د_._ا_._‏_-;\-* #,##0.000\ _د_._ا_._‏_-;_-* &quot;-&quot;???\ _د_._ا_._‏_-;_-@_-"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color indexed="8"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="19" formatCode="dd/mm/yyyy"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color indexed="8"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color indexed="8"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color indexed="8"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color indexed="8"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color indexed="8"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="19" formatCode="dd/mm/yyyy"/>
+    </dxf>
     <dxf>
       <numFmt numFmtId="164" formatCode="_-* #,##0.000\ _د_._ا_._‏_-;\-* #,##0.000\ _د_._ا_._‏_-;_-* &quot;-&quot;???\ _د_._ا_._‏_-;_-@_-"/>
     </dxf>
@@ -452,9 +633,6 @@
         <scheme val="minor"/>
       </font>
       <numFmt numFmtId="164" formatCode="_-* #,##0.000\ _د_._ا_._‏_-;\-* #,##0.000\ _د_._ا_._‏_-;_-* &quot;-&quot;???\ _د_._ا_._‏_-;_-@_-"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="19" formatCode="dd/mm/yyyy"/>
     </dxf>
     <dxf>
       <font>
@@ -589,25 +767,25 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Table1" displayName="Table1" ref="A1:M257" totalsRowShown="0" headerRowDxfId="13">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Table1" displayName="Table1" ref="A1:M258" totalsRowCount="1" headerRowDxfId="26">
   <autoFilter ref="A1:M257" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:M257">
     <sortCondition ref="F1:F257"/>
   </sortState>
   <tableColumns count="13">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="الرقم" dataDxfId="12"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="رقم الموظف /رقم البطاقة" dataDxfId="11"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="اسم المريض" dataDxfId="10"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="رقم النموذج" dataDxfId="9"/>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="نوع المستفيد" dataDxfId="8"/>
-    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="تاريخ البيع" dataDxfId="7"/>
-    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0000-000007000000}" name="قيمة الفاتورة" dataDxfId="5"/>
-    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0000-000008000000}" name="قيمة المشاركة" dataDxfId="4"/>
-    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0000-000009000000}" name="صافي القيمة" dataDxfId="3"/>
-    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0000-00000A000000}" name="القيمة المطلوبة" dataDxfId="2"/>
-    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0000-00000B000000}" name="المدفوع" dataDxfId="1"/>
-    <tableColumn id="12" xr3:uid="{00000000-0010-0000-0000-00000C000000}" name="المتبقي" dataDxfId="0"/>
-    <tableColumn id="13" xr3:uid="{041AFAF5-9550-455C-B55D-99C85FD7E974}" name="تاريخ الدفعة" dataDxfId="6"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="الرقم" dataDxfId="25" totalsRowDxfId="12"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="رقم الموظف /رقم البطاقة" dataDxfId="24" totalsRowDxfId="11"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="اسم المريض" dataDxfId="23" totalsRowDxfId="10"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="رقم النموذج" dataDxfId="22" totalsRowDxfId="9"/>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="نوع المستفيد" dataDxfId="21" totalsRowDxfId="8"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="تاريخ البيع" dataDxfId="20" totalsRowDxfId="7"/>
+    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0000-000007000000}" name="قيمة الفاتورة" dataDxfId="19" totalsRowDxfId="6"/>
+    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0000-000008000000}" name="قيمة المشاركة" dataDxfId="18" totalsRowDxfId="5"/>
+    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0000-000009000000}" name="صافي القيمة" dataDxfId="17" totalsRowDxfId="4"/>
+    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0000-00000A000000}" name="القيمة المطلوبة" dataDxfId="16" totalsRowDxfId="3"/>
+    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0000-00000B000000}" name="المدفوع" totalsRowFunction="sum" dataDxfId="15" totalsRowDxfId="2"/>
+    <tableColumn id="12" xr3:uid="{00000000-0010-0000-0000-00000C000000}" name="المتبقي" dataDxfId="14" totalsRowDxfId="1"/>
+    <tableColumn id="13" xr3:uid="{041AFAF5-9550-455C-B55D-99C85FD7E974}" name="تاريخ الدفعة" dataDxfId="13" totalsRowDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium3" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -930,7 +1108,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:M257"/>
+  <dimension ref="A1:M258"/>
   <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="5.19921875" customWidth="1"/>
@@ -1018,14 +1196,14 @@
         <v>30.103999999999999</v>
       </c>
       <c r="J2" s="7">
-        <f>G2*0.94-H2</f>
+        <f t="shared" ref="J2:J65" si="0">G2*0.94-H2</f>
         <v>27.8462</v>
       </c>
       <c r="K2" s="7">
         <v>27.846</v>
       </c>
       <c r="L2" s="7">
-        <f>J2-K2</f>
+        <f t="shared" ref="L2:L65" si="1">J2-K2</f>
         <v>1.9999999999953388E-4</v>
       </c>
       <c r="M2" s="4">
@@ -1061,14 +1239,14 @@
         <v>37.896000000000001</v>
       </c>
       <c r="J3" s="7">
-        <f>G3*0.94-H3</f>
+        <f t="shared" si="0"/>
         <v>35.053799999999995</v>
       </c>
       <c r="K3" s="7">
         <v>35.052999999999997</v>
       </c>
       <c r="L3" s="7">
-        <f>J3-K3</f>
+        <f t="shared" si="1"/>
         <v>7.9999999999813554E-4</v>
       </c>
       <c r="M3" s="4">
@@ -1104,14 +1282,14 @@
         <v>93.896000000000001</v>
       </c>
       <c r="J4" s="7">
-        <f>G4*0.94-H4</f>
+        <f t="shared" si="0"/>
         <v>86.853799999999993</v>
       </c>
       <c r="K4" s="7">
         <v>86.852999999999994</v>
       </c>
       <c r="L4" s="7">
-        <f>J4-K4</f>
+        <f t="shared" si="1"/>
         <v>7.9999999999813554E-4</v>
       </c>
       <c r="M4" s="4">
@@ -1147,14 +1325,14 @@
         <v>80.968000000000004</v>
       </c>
       <c r="J5" s="7">
-        <f>G5*0.94-H5</f>
+        <f t="shared" si="0"/>
         <v>74.895399999999981</v>
       </c>
       <c r="K5" s="7">
         <v>74.896000000000001</v>
       </c>
       <c r="L5" s="7">
-        <f>J5-K5</f>
+        <f t="shared" si="1"/>
         <v>-6.0000000001991793E-4</v>
       </c>
       <c r="M5" s="4">
@@ -1190,14 +1368,14 @@
         <v>132.66399999999999</v>
       </c>
       <c r="J6" s="7">
-        <f>G6*0.94-H6</f>
+        <f t="shared" si="0"/>
         <v>122.71420000000001</v>
       </c>
       <c r="K6" s="7">
         <v>122.71599999999999</v>
       </c>
       <c r="L6" s="7">
-        <f>J6-K6</f>
+        <f t="shared" si="1"/>
         <v>-1.7999999999886995E-3</v>
       </c>
       <c r="M6" s="4">
@@ -1233,14 +1411,14 @@
         <v>56.96</v>
       </c>
       <c r="J7" s="7">
-        <f>G7*0.94-H7</f>
+        <f t="shared" si="0"/>
         <v>52.687999999999995</v>
       </c>
       <c r="K7" s="7">
         <v>52.688000000000002</v>
       </c>
       <c r="L7" s="7">
-        <f>J7-K7</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="M7" s="4">
@@ -1276,14 +1454,14 @@
         <v>42.048000000000002</v>
       </c>
       <c r="J8" s="7">
-        <f>G8*0.94-H8</f>
+        <f t="shared" si="0"/>
         <v>38.894399999999997</v>
       </c>
       <c r="K8" s="7">
         <v>38.893999999999998</v>
       </c>
       <c r="L8" s="7">
-        <f>J8-K8</f>
+        <f t="shared" si="1"/>
         <v>3.9999999999906777E-4</v>
       </c>
       <c r="M8" s="4">
@@ -1319,14 +1497,14 @@
         <v>33.04</v>
       </c>
       <c r="J9" s="7">
-        <f>G9*0.94-H9</f>
+        <f t="shared" si="0"/>
         <v>30.561999999999998</v>
       </c>
       <c r="K9" s="7">
         <v>28.91</v>
       </c>
       <c r="L9" s="7">
-        <f>J9-K9</f>
+        <f t="shared" si="1"/>
         <v>1.6519999999999975</v>
       </c>
       <c r="M9" s="4">
@@ -1362,14 +1540,14 @@
         <v>29.712</v>
       </c>
       <c r="J10" s="7">
-        <f>G10*0.94-H10</f>
+        <f t="shared" si="0"/>
         <v>27.483599999999999</v>
       </c>
       <c r="K10" s="7">
         <v>27.483000000000001</v>
       </c>
       <c r="L10" s="7">
-        <f>J10-K10</f>
+        <f t="shared" si="1"/>
         <v>5.9999999999860165E-4</v>
       </c>
       <c r="M10" s="4">
@@ -1405,14 +1583,14 @@
         <v>30.103999999999999</v>
       </c>
       <c r="J11" s="7">
-        <f>G11*0.94-H11</f>
+        <f t="shared" si="0"/>
         <v>27.8462</v>
       </c>
       <c r="K11" s="7">
         <v>27.846</v>
       </c>
       <c r="L11" s="7">
-        <f>J11-K11</f>
+        <f t="shared" si="1"/>
         <v>1.9999999999953388E-4</v>
       </c>
       <c r="M11" s="4">
@@ -1448,14 +1626,14 @@
         <v>36.031999999999996</v>
       </c>
       <c r="J12" s="7">
-        <f>G12*0.94-H12</f>
+        <f t="shared" si="0"/>
         <v>33.329599999999999</v>
       </c>
       <c r="K12" s="7">
         <v>33.33</v>
       </c>
       <c r="L12" s="7">
-        <f>J12-K12</f>
+        <f t="shared" si="1"/>
         <v>-3.9999999999906777E-4</v>
       </c>
       <c r="M12" s="4">
@@ -1491,14 +1669,14 @@
         <v>93.896000000000001</v>
       </c>
       <c r="J13" s="7">
-        <f>G13*0.94-H13</f>
+        <f t="shared" si="0"/>
         <v>86.853799999999993</v>
       </c>
       <c r="K13" s="7">
         <v>86.852999999999994</v>
       </c>
       <c r="L13" s="7">
-        <f>J13-K13</f>
+        <f t="shared" si="1"/>
         <v>7.9999999999813554E-4</v>
       </c>
       <c r="M13" s="4">
@@ -1534,14 +1712,14 @@
         <v>80.968000000000004</v>
       </c>
       <c r="J14" s="7">
-        <f>G14*0.94-H14</f>
+        <f t="shared" si="0"/>
         <v>74.895399999999981</v>
       </c>
       <c r="K14" s="7">
         <v>74.896000000000001</v>
       </c>
       <c r="L14" s="7">
-        <f>J14-K14</f>
+        <f t="shared" si="1"/>
         <v>-6.0000000001991793E-4</v>
       </c>
       <c r="M14" s="4">
@@ -1577,14 +1755,14 @@
         <v>134.28800000000001</v>
       </c>
       <c r="J15" s="7">
-        <f>G15*0.94-H15</f>
+        <f t="shared" si="0"/>
         <v>124.21639999999999</v>
       </c>
       <c r="K15" s="7">
         <v>124.218</v>
       </c>
       <c r="L15" s="7">
-        <f>J15-K15</f>
+        <f t="shared" si="1"/>
         <v>-1.6000000000104819E-3</v>
       </c>
       <c r="M15" s="4">
@@ -1620,14 +1798,14 @@
         <v>56.96</v>
       </c>
       <c r="J16" s="7">
-        <f>G16*0.94-H16</f>
+        <f t="shared" si="0"/>
         <v>52.687999999999995</v>
       </c>
       <c r="K16" s="7">
         <v>52.688000000000002</v>
       </c>
       <c r="L16" s="7">
-        <f>J16-K16</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="M16" s="4">
@@ -1663,14 +1841,14 @@
         <v>24.192</v>
       </c>
       <c r="J17" s="7">
-        <f>G17*0.94-H17</f>
+        <f t="shared" si="0"/>
         <v>22.377599999999994</v>
       </c>
       <c r="K17" s="7">
         <v>21.167999999999999</v>
       </c>
       <c r="L17" s="7">
-        <f>J17-K17</f>
+        <f t="shared" si="1"/>
         <v>1.2095999999999947</v>
       </c>
       <c r="M17" s="4">
@@ -1706,14 +1884,14 @@
         <v>41.951999999999998</v>
       </c>
       <c r="J18" s="7">
-        <f>G18*0.94-H18</f>
+        <f t="shared" si="0"/>
         <v>38.805599999999998</v>
       </c>
       <c r="K18" s="7">
         <v>38.805</v>
       </c>
       <c r="L18" s="7">
-        <f>J18-K18</f>
+        <f t="shared" si="1"/>
         <v>5.9999999999860165E-4</v>
       </c>
       <c r="M18" s="4">
@@ -1749,14 +1927,14 @@
         <v>36.159999999999997</v>
       </c>
       <c r="J19" s="7">
-        <f>G19*0.94-H19</f>
+        <f t="shared" si="0"/>
         <v>33.448</v>
       </c>
       <c r="K19" s="6">
         <v>33.447000000000003</v>
       </c>
       <c r="L19" s="7">
-        <f>J19-K19</f>
+        <f t="shared" si="1"/>
         <v>9.9999999999766942E-4</v>
       </c>
       <c r="M19" s="4">
@@ -1792,14 +1970,14 @@
         <v>30.103999999999999</v>
       </c>
       <c r="J20" s="7">
-        <f>G20*0.94-H20</f>
+        <f t="shared" si="0"/>
         <v>27.8462</v>
       </c>
       <c r="K20" s="7">
         <v>27.846</v>
       </c>
       <c r="L20" s="7">
-        <f>J20-K20</f>
+        <f t="shared" si="1"/>
         <v>1.9999999999953388E-4</v>
       </c>
       <c r="M20" s="4">
@@ -1835,14 +2013,14 @@
         <v>19.024000000000001</v>
       </c>
       <c r="J21" s="7">
-        <f>G21*0.94-H21</f>
+        <f t="shared" si="0"/>
         <v>17.597200000000001</v>
       </c>
       <c r="K21" s="7">
         <v>17.600999999999999</v>
       </c>
       <c r="L21" s="7">
-        <f>J21-K21</f>
+        <f t="shared" si="1"/>
         <v>-3.7999999999982492E-3</v>
       </c>
       <c r="M21" s="4">
@@ -1878,14 +2056,14 @@
         <v>18.504000000000001</v>
       </c>
       <c r="J22" s="7">
-        <f>G22*0.94-H22</f>
+        <f t="shared" si="0"/>
         <v>17.116199999999996</v>
       </c>
       <c r="K22" s="7">
         <v>17.114999999999998</v>
       </c>
       <c r="L22" s="7">
-        <f>J22-K22</f>
+        <f t="shared" si="1"/>
         <v>1.1999999999972033E-3</v>
       </c>
       <c r="M22" s="4">
@@ -1921,14 +2099,14 @@
         <v>93.896000000000001</v>
       </c>
       <c r="J23" s="7">
-        <f>G23*0.94-H23</f>
+        <f t="shared" si="0"/>
         <v>86.853799999999993</v>
       </c>
       <c r="K23" s="7">
         <v>86.852999999999994</v>
       </c>
       <c r="L23" s="7">
-        <f>J23-K23</f>
+        <f t="shared" si="1"/>
         <v>7.9999999999813554E-4</v>
       </c>
       <c r="M23" s="4">
@@ -1964,14 +2142,14 @@
         <v>134.28800000000001</v>
       </c>
       <c r="J24" s="7">
-        <f>G24*0.94-H24</f>
+        <f t="shared" si="0"/>
         <v>124.21639999999999</v>
       </c>
       <c r="K24" s="7">
         <v>124.218</v>
       </c>
       <c r="L24" s="7">
-        <f>J24-K24</f>
+        <f t="shared" si="1"/>
         <v>-1.6000000000104819E-3</v>
       </c>
       <c r="M24" s="4">
@@ -2007,14 +2185,14 @@
         <v>56.96</v>
       </c>
       <c r="J25" s="7">
-        <f>G25*0.94-H25</f>
+        <f t="shared" si="0"/>
         <v>52.687999999999995</v>
       </c>
       <c r="K25" s="7">
         <v>52.688000000000002</v>
       </c>
       <c r="L25" s="7">
-        <f>J25-K25</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="M25" s="4">
@@ -2050,14 +2228,14 @@
         <v>80.968000000000004</v>
       </c>
       <c r="J26" s="7">
-        <f>G26*0.94-H26</f>
+        <f t="shared" si="0"/>
         <v>74.895399999999981</v>
       </c>
       <c r="K26" s="7">
         <v>74.896000000000001</v>
       </c>
       <c r="L26" s="7">
-        <f>J26-K26</f>
+        <f t="shared" si="1"/>
         <v>-6.0000000001991793E-4</v>
       </c>
       <c r="M26" s="4">
@@ -2093,14 +2271,14 @@
         <v>41.048000000000002</v>
       </c>
       <c r="J27" s="7">
-        <f>G27*0.94-H27</f>
+        <f t="shared" si="0"/>
         <v>37.9694</v>
       </c>
       <c r="K27" s="7">
         <v>37.942</v>
       </c>
       <c r="L27" s="7">
-        <f>J27-K27</f>
+        <f t="shared" si="1"/>
         <v>2.7400000000000091E-2</v>
       </c>
       <c r="M27" s="4">
@@ -2136,11 +2314,11 @@
         <v>37.375999999999998</v>
       </c>
       <c r="J28" s="7">
-        <f>G28*0.94-H28</f>
+        <f t="shared" si="0"/>
         <v>34.572799999999994</v>
       </c>
       <c r="L28" s="7">
-        <f>J28-K28</f>
+        <f t="shared" si="1"/>
         <v>34.572799999999994</v>
       </c>
       <c r="M28" s="4"/>
@@ -2174,14 +2352,14 @@
         <v>24.4</v>
       </c>
       <c r="J29" s="7">
-        <f>G29*0.94-H29</f>
+        <f t="shared" si="0"/>
         <v>22.57</v>
       </c>
       <c r="K29" s="7">
         <v>22.57</v>
       </c>
       <c r="L29" s="7">
-        <f>J29-K29</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="M29" s="4">
@@ -2217,14 +2395,14 @@
         <v>33.231999999999999</v>
       </c>
       <c r="J30" s="7">
-        <f>G30*0.94-H30</f>
+        <f t="shared" si="0"/>
         <v>30.739599999999996</v>
       </c>
       <c r="K30" s="7">
         <v>30.74</v>
       </c>
       <c r="L30" s="7">
-        <f>J30-K30</f>
+        <f t="shared" si="1"/>
         <v>-4.0000000000262048E-4</v>
       </c>
       <c r="M30" s="4">
@@ -2260,14 +2438,14 @@
         <v>117.568</v>
       </c>
       <c r="J31" s="7">
-        <f>G31*0.94-H31</f>
+        <f t="shared" si="0"/>
         <v>108.75040000000001</v>
       </c>
       <c r="K31" s="7">
         <v>108.751</v>
       </c>
       <c r="L31" s="7">
-        <f>J31-K31</f>
+        <f t="shared" si="1"/>
         <v>-5.9999999999149622E-4</v>
       </c>
       <c r="M31" s="4">
@@ -2303,14 +2481,14 @@
         <v>197.84800000000001</v>
       </c>
       <c r="J32" s="7">
-        <f>G32*0.94-H32</f>
+        <f t="shared" si="0"/>
         <v>183.00939999999997</v>
       </c>
       <c r="K32" s="7">
         <v>183.01</v>
       </c>
       <c r="L32" s="7">
-        <f>J32-K32</f>
+        <f t="shared" si="1"/>
         <v>-6.0000000001991793E-4</v>
       </c>
       <c r="M32" s="4">
@@ -2346,14 +2524,14 @@
         <v>58.664000000000001</v>
       </c>
       <c r="J33" s="7">
-        <f>G33*0.94-H33</f>
+        <f t="shared" si="0"/>
         <v>54.264200000000002</v>
       </c>
       <c r="K33" s="7">
         <v>54.265000000000001</v>
       </c>
       <c r="L33" s="7">
-        <f>J33-K33</f>
+        <f t="shared" si="1"/>
         <v>-7.9999999999813554E-4</v>
       </c>
       <c r="M33" s="4">
@@ -2389,14 +2567,14 @@
         <v>115.98399999999999</v>
       </c>
       <c r="J34" s="7">
-        <f>G34*0.94-H34</f>
+        <f t="shared" si="0"/>
         <v>107.28519999999999</v>
       </c>
       <c r="K34" s="7">
         <v>107.285</v>
       </c>
       <c r="L34" s="7">
-        <f>J34-K34</f>
+        <f t="shared" si="1"/>
         <v>1.9999999999242846E-4</v>
       </c>
       <c r="M34" s="4">
@@ -2432,14 +2610,14 @@
         <v>26.76</v>
       </c>
       <c r="J35" s="7">
-        <f>G35*0.94-H35</f>
+        <f t="shared" si="0"/>
         <v>24.753</v>
       </c>
       <c r="K35" s="7">
         <v>24.751999999999999</v>
       </c>
       <c r="L35" s="7">
-        <f>J35-K35</f>
+        <f t="shared" si="1"/>
         <v>1.0000000000012221E-3</v>
       </c>
       <c r="M35" s="4">
@@ -2475,11 +2653,11 @@
         <v>37.375999999999998</v>
       </c>
       <c r="J36" s="7">
-        <f>G36*0.94-H36</f>
+        <f t="shared" si="0"/>
         <v>34.572799999999994</v>
       </c>
       <c r="L36" s="7">
-        <f>J36-K36</f>
+        <f t="shared" si="1"/>
         <v>34.572799999999994</v>
       </c>
       <c r="M36" s="4"/>
@@ -2513,14 +2691,14 @@
         <v>25.128</v>
       </c>
       <c r="J37" s="7">
-        <f>G37*0.94-H37</f>
+        <f t="shared" si="0"/>
         <v>23.243399999999998</v>
       </c>
       <c r="K37" s="7">
         <v>23.242999999999999</v>
       </c>
       <c r="L37" s="7">
-        <f>J37-K37</f>
+        <f t="shared" si="1"/>
         <v>3.9999999999906777E-4</v>
       </c>
       <c r="M37" s="4">
@@ -2556,14 +2734,14 @@
         <v>31.56</v>
       </c>
       <c r="J38" s="7">
-        <f>G38*0.94-H38</f>
+        <f t="shared" si="0"/>
         <v>29.192999999999998</v>
       </c>
       <c r="K38" s="7">
         <v>29.193000000000001</v>
       </c>
       <c r="L38" s="7">
-        <f>J38-K38</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="M38" s="4">
@@ -2599,14 +2777,14 @@
         <v>30.103999999999999</v>
       </c>
       <c r="J39" s="7">
-        <f>G39*0.94-H39</f>
+        <f t="shared" si="0"/>
         <v>27.8462</v>
       </c>
       <c r="K39" s="7">
         <v>27.846</v>
       </c>
       <c r="L39" s="7">
-        <f>J39-K39</f>
+        <f t="shared" si="1"/>
         <v>1.9999999999953388E-4</v>
       </c>
       <c r="M39" s="4">
@@ -2642,14 +2820,14 @@
         <v>80.968000000000004</v>
       </c>
       <c r="J40" s="7">
-        <f>G40*0.94-H40</f>
+        <f t="shared" si="0"/>
         <v>74.895399999999981</v>
       </c>
       <c r="K40" s="7">
         <v>74.896000000000001</v>
       </c>
       <c r="L40" s="7">
-        <f>J40-K40</f>
+        <f t="shared" si="1"/>
         <v>-6.0000000001991793E-4</v>
       </c>
       <c r="M40" s="4">
@@ -2685,14 +2863,14 @@
         <v>132.66399999999999</v>
       </c>
       <c r="J41" s="7">
-        <f>G41*0.94-H41</f>
+        <f t="shared" si="0"/>
         <v>122.71420000000001</v>
       </c>
       <c r="K41" s="7">
         <v>122.71599999999999</v>
       </c>
       <c r="L41" s="7">
-        <f>J41-K41</f>
+        <f t="shared" si="1"/>
         <v>-1.7999999999886995E-3</v>
       </c>
       <c r="M41" s="4">
@@ -2728,14 +2906,14 @@
         <v>56.96</v>
       </c>
       <c r="J42" s="7">
-        <f>G42*0.94-H42</f>
+        <f t="shared" si="0"/>
         <v>52.687999999999995</v>
       </c>
       <c r="K42" s="7">
         <v>52.688000000000002</v>
       </c>
       <c r="L42" s="7">
-        <f>J42-K42</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="M42" s="4">
@@ -2771,14 +2949,14 @@
         <v>93.896000000000001</v>
       </c>
       <c r="J43" s="7">
-        <f>G43*0.94-H43</f>
+        <f t="shared" si="0"/>
         <v>86.853799999999993</v>
       </c>
       <c r="K43" s="7">
         <v>86.852999999999994</v>
       </c>
       <c r="L43" s="7">
-        <f>J43-K43</f>
+        <f t="shared" si="1"/>
         <v>7.9999999999813554E-4</v>
       </c>
       <c r="M43" s="4">
@@ -2814,11 +2992,11 @@
         <v>25.224</v>
       </c>
       <c r="J44" s="7">
-        <f>G44*0.94-H44</f>
+        <f t="shared" si="0"/>
         <v>23.332199999999997</v>
       </c>
       <c r="L44" s="7">
-        <f>J44-K44</f>
+        <f t="shared" si="1"/>
         <v>23.332199999999997</v>
       </c>
       <c r="M44" s="4"/>
@@ -2852,14 +3030,14 @@
         <v>40.664000000000001</v>
       </c>
       <c r="J45" s="7">
-        <f>G45*0.94-H45</f>
+        <f t="shared" si="0"/>
         <v>37.614199999999997</v>
       </c>
       <c r="K45" s="7">
         <v>37.613999999999997</v>
       </c>
       <c r="L45" s="7">
-        <f>J45-K45</f>
+        <f t="shared" si="1"/>
         <v>1.9999999999953388E-4</v>
       </c>
       <c r="M45" s="4">
@@ -2895,14 +3073,14 @@
         <v>18.192</v>
       </c>
       <c r="J46" s="7">
-        <f>G46*0.94-H46</f>
+        <f t="shared" si="0"/>
         <v>16.827599999999997</v>
       </c>
       <c r="K46" s="7">
         <v>16.96</v>
       </c>
       <c r="L46" s="7">
-        <f>J46-K46</f>
+        <f t="shared" si="1"/>
         <v>-0.13240000000000407</v>
       </c>
       <c r="M46" s="4">
@@ -2938,14 +3116,14 @@
         <v>18.335999999999999</v>
       </c>
       <c r="J47" s="7">
-        <f>G47*0.94-H47</f>
+        <f t="shared" si="0"/>
         <v>16.960799999999999</v>
       </c>
       <c r="K47" s="7">
         <v>16.827999999999999</v>
       </c>
       <c r="L47" s="7">
-        <f>J47-K47</f>
+        <f t="shared" si="1"/>
         <v>0.13279999999999959</v>
       </c>
       <c r="M47" s="4">
@@ -2981,14 +3159,14 @@
         <v>26.327999999999999</v>
       </c>
       <c r="J48" s="7">
-        <f>G48*0.94-H48</f>
+        <f t="shared" si="0"/>
         <v>24.353399999999993</v>
       </c>
       <c r="K48" s="7">
         <v>24.353000000000002</v>
       </c>
       <c r="L48" s="7">
-        <f>J48-K48</f>
+        <f t="shared" si="1"/>
         <v>3.9999999999196234E-4</v>
       </c>
       <c r="M48" s="4">
@@ -3024,14 +3202,14 @@
         <v>5.1040000000000001</v>
       </c>
       <c r="J49" s="7">
-        <f>G49*0.94-H49</f>
+        <f t="shared" si="0"/>
         <v>4.7211999999999996</v>
       </c>
       <c r="K49" s="7">
         <v>4.7210000000000001</v>
       </c>
       <c r="L49" s="7">
-        <f>J49-K49</f>
+        <f t="shared" si="1"/>
         <v>1.9999999999953388E-4</v>
       </c>
       <c r="M49" s="4">
@@ -3067,14 +3245,14 @@
         <v>30.103999999999999</v>
       </c>
       <c r="J50" s="7">
-        <f>G50*0.94-H50</f>
+        <f t="shared" si="0"/>
         <v>27.8462</v>
       </c>
       <c r="K50" s="7">
         <v>27.846</v>
       </c>
       <c r="L50" s="7">
-        <f>J50-K50</f>
+        <f t="shared" si="1"/>
         <v>1.9999999999953388E-4</v>
       </c>
       <c r="M50" s="4">
@@ -3110,11 +3288,11 @@
         <v>34.76</v>
       </c>
       <c r="J51" s="7">
-        <f>G51*0.94-H51</f>
+        <f t="shared" si="0"/>
         <v>32.153000000000006</v>
       </c>
       <c r="L51" s="7">
-        <f>J51-K51</f>
+        <f t="shared" si="1"/>
         <v>32.153000000000006</v>
       </c>
       <c r="M51" s="4"/>
@@ -3148,14 +3326,14 @@
         <v>88.623999999999995</v>
       </c>
       <c r="J52" s="7">
-        <f>G52*0.94-H52</f>
+        <f t="shared" si="0"/>
         <v>81.977200000000011</v>
       </c>
       <c r="K52" s="7">
         <v>81.977000000000004</v>
       </c>
       <c r="L52" s="7">
-        <f>J52-K52</f>
+        <f t="shared" si="1"/>
         <v>2.0000000000663931E-4</v>
       </c>
       <c r="M52" s="4">
@@ -3191,14 +3369,14 @@
         <v>80.968000000000004</v>
       </c>
       <c r="J53" s="7">
-        <f>G53*0.94-H53</f>
+        <f t="shared" si="0"/>
         <v>74.895399999999981</v>
       </c>
       <c r="K53" s="7">
         <v>74.896000000000001</v>
       </c>
       <c r="L53" s="7">
-        <f>J53-K53</f>
+        <f t="shared" si="1"/>
         <v>-6.0000000001991793E-4</v>
       </c>
       <c r="M53" s="4">
@@ -3234,14 +3412,14 @@
         <v>56.96</v>
       </c>
       <c r="J54" s="7">
-        <f>G54*0.94-H54</f>
+        <f t="shared" si="0"/>
         <v>52.687999999999995</v>
       </c>
       <c r="K54" s="7">
         <v>52.688000000000002</v>
       </c>
       <c r="L54" s="7">
-        <f>J54-K54</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="M54" s="4">
@@ -3277,14 +3455,14 @@
         <v>134.28800000000001</v>
       </c>
       <c r="J55" s="7">
-        <f>G55*0.94-H55</f>
+        <f t="shared" si="0"/>
         <v>124.21639999999999</v>
       </c>
       <c r="K55" s="7">
         <v>124.218</v>
       </c>
       <c r="L55" s="7">
-        <f>J55-K55</f>
+        <f t="shared" si="1"/>
         <v>-1.6000000000104819E-3</v>
       </c>
       <c r="M55" s="4">
@@ -3320,14 +3498,14 @@
         <v>29.744</v>
       </c>
       <c r="J56" s="7">
-        <f>G56*0.94-H56</f>
+        <f t="shared" si="0"/>
         <v>27.513199999999998</v>
       </c>
       <c r="K56" s="7">
         <v>27.513000000000002</v>
       </c>
       <c r="L56" s="7">
-        <f>J56-K56</f>
+        <f t="shared" si="1"/>
         <v>1.9999999999598117E-4</v>
       </c>
       <c r="M56" s="4">
@@ -3363,14 +3541,14 @@
         <v>22.456</v>
       </c>
       <c r="J57" s="7">
-        <f>G57*0.94-H57</f>
+        <f t="shared" si="0"/>
         <v>20.771799999999999</v>
       </c>
       <c r="K57" s="7">
         <v>20.762</v>
       </c>
       <c r="L57" s="7">
-        <f>J57-K57</f>
+        <f t="shared" si="1"/>
         <v>9.7999999999984766E-3</v>
       </c>
       <c r="M57" s="4">
@@ -3406,11 +3584,11 @@
         <v>24.547999999999998</v>
       </c>
       <c r="J58" s="7">
-        <f>G58*0.94-H58</f>
+        <f t="shared" si="0"/>
         <v>22.815199999999997</v>
       </c>
       <c r="L58" s="7">
-        <f>J58-K58</f>
+        <f t="shared" si="1"/>
         <v>22.815199999999997</v>
       </c>
       <c r="M58" s="4"/>
@@ -3444,14 +3622,14 @@
         <v>39.488</v>
       </c>
       <c r="J59" s="7">
-        <f>G59*0.94-H59</f>
+        <f t="shared" si="0"/>
         <v>36.526399999999995</v>
       </c>
       <c r="K59" s="7">
         <v>36.526000000000003</v>
       </c>
       <c r="L59" s="7">
-        <f>J59-K59</f>
+        <f t="shared" si="1"/>
         <v>3.9999999999196234E-4</v>
       </c>
       <c r="M59" s="4">
@@ -3487,14 +3665,14 @@
         <v>30.103999999999999</v>
       </c>
       <c r="J60" s="7">
-        <f>G60*0.94-H60</f>
+        <f t="shared" si="0"/>
         <v>27.8462</v>
       </c>
       <c r="K60" s="7">
         <v>27.846</v>
       </c>
       <c r="L60" s="7">
-        <f>J60-K60</f>
+        <f t="shared" si="1"/>
         <v>1.9999999999953388E-4</v>
       </c>
       <c r="M60" s="4">
@@ -3530,11 +3708,11 @@
         <v>33.904000000000003</v>
       </c>
       <c r="J61" s="7">
-        <f>G61*0.94-H61</f>
+        <f t="shared" si="0"/>
         <v>31.361200000000004</v>
       </c>
       <c r="L61" s="7">
-        <f>J61-K61</f>
+        <f t="shared" si="1"/>
         <v>31.361200000000004</v>
       </c>
       <c r="M61" s="4"/>
@@ -3568,14 +3746,14 @@
         <v>93.896000000000001</v>
       </c>
       <c r="J62" s="7">
-        <f>G62*0.94-H62</f>
+        <f t="shared" si="0"/>
         <v>86.853799999999993</v>
       </c>
       <c r="K62" s="7">
         <v>86.852999999999994</v>
       </c>
       <c r="L62" s="7">
-        <f>J62-K62</f>
+        <f t="shared" si="1"/>
         <v>7.9999999999813554E-4</v>
       </c>
       <c r="M62" s="4">
@@ -3611,14 +3789,14 @@
         <v>80.968000000000004</v>
       </c>
       <c r="J63" s="7">
-        <f>G63*0.94-H63</f>
+        <f t="shared" si="0"/>
         <v>74.895399999999981</v>
       </c>
       <c r="K63" s="7">
         <v>74.896000000000001</v>
       </c>
       <c r="L63" s="7">
-        <f>J63-K63</f>
+        <f t="shared" si="1"/>
         <v>-6.0000000001991793E-4</v>
       </c>
       <c r="M63" s="4">
@@ -3654,14 +3832,14 @@
         <v>134.28800000000001</v>
       </c>
       <c r="J64" s="7">
-        <f>G64*0.94-H64</f>
+        <f t="shared" si="0"/>
         <v>124.21639999999999</v>
       </c>
       <c r="K64" s="7">
         <v>124.218</v>
       </c>
       <c r="L64" s="7">
-        <f>J64-K64</f>
+        <f t="shared" si="1"/>
         <v>-1.6000000000104819E-3</v>
       </c>
       <c r="M64" s="4">
@@ -3697,14 +3875,14 @@
         <v>56.96</v>
       </c>
       <c r="J65" s="7">
-        <f>G65*0.94-H65</f>
+        <f t="shared" si="0"/>
         <v>52.687999999999995</v>
       </c>
       <c r="K65" s="7">
         <v>52.688000000000002</v>
       </c>
       <c r="L65" s="7">
-        <f>J65-K65</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="M65" s="4">
@@ -3740,14 +3918,14 @@
         <v>42.048000000000002</v>
       </c>
       <c r="J66" s="7">
-        <f>G66*0.94-H66</f>
+        <f t="shared" ref="J66:J129" si="2">G66*0.94-H66</f>
         <v>38.894399999999997</v>
       </c>
       <c r="K66" s="7">
         <v>38.893999999999998</v>
       </c>
       <c r="L66" s="7">
-        <f>J66-K66</f>
+        <f t="shared" ref="L66:L129" si="3">J66-K66</f>
         <v>3.9999999999906777E-4</v>
       </c>
       <c r="M66" s="4">
@@ -3783,14 +3961,14 @@
         <v>15.53</v>
       </c>
       <c r="J67" s="7">
-        <f>G67*0.94-H67</f>
+        <f t="shared" si="2"/>
         <v>14.598199999999999</v>
       </c>
       <c r="K67" s="7">
         <v>12.372</v>
       </c>
       <c r="L67" s="7">
-        <f>J67-K67</f>
+        <f t="shared" si="3"/>
         <v>2.2261999999999986</v>
       </c>
       <c r="M67" s="4">
@@ -3826,14 +4004,14 @@
         <v>5.84</v>
       </c>
       <c r="J68" s="7">
-        <f>G68*0.94-H68</f>
+        <f t="shared" si="2"/>
         <v>5.4019999999999992</v>
       </c>
       <c r="K68" s="7">
         <v>5.4020000000000001</v>
       </c>
       <c r="L68" s="7">
-        <f>J68-K68</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="M68" s="4">
@@ -3869,14 +4047,14 @@
         <v>45.856000000000002</v>
       </c>
       <c r="J69" s="7">
-        <f>G69*0.94-H69</f>
+        <f t="shared" si="2"/>
         <v>42.416800000000002</v>
       </c>
       <c r="K69" s="7">
         <v>42.417000000000002</v>
       </c>
       <c r="L69" s="7">
-        <f>J69-K69</f>
+        <f t="shared" si="3"/>
         <v>-1.9999999999953388E-4</v>
       </c>
       <c r="M69" s="4">
@@ -3912,14 +4090,14 @@
         <v>34.768000000000001</v>
       </c>
       <c r="J70" s="7">
-        <f>G70*0.94-H70</f>
+        <f t="shared" si="2"/>
         <v>32.160399999999996</v>
       </c>
       <c r="K70" s="7">
         <v>32.161000000000001</v>
       </c>
       <c r="L70" s="7">
-        <f>J70-K70</f>
+        <f t="shared" si="3"/>
         <v>-6.0000000000570708E-4</v>
       </c>
       <c r="M70" s="4">
@@ -3955,14 +4133,14 @@
         <v>17.704000000000001</v>
       </c>
       <c r="J71" s="7">
-        <f>G71*0.94-H71</f>
+        <f t="shared" si="2"/>
         <v>16.376199999999997</v>
       </c>
       <c r="K71" s="7">
         <v>16.376000000000001</v>
       </c>
       <c r="L71" s="7">
-        <f>J71-K71</f>
+        <f t="shared" si="3"/>
         <v>1.9999999999598117E-4</v>
       </c>
       <c r="M71" s="4">
@@ -3998,14 +4176,14 @@
         <v>30.103999999999999</v>
       </c>
       <c r="J72" s="7">
-        <f>G72*0.94-H72</f>
+        <f t="shared" si="2"/>
         <v>27.8462</v>
       </c>
       <c r="K72" s="7">
         <v>27.846</v>
       </c>
       <c r="L72" s="7">
-        <f>J72-K72</f>
+        <f t="shared" si="3"/>
         <v>1.9999999999953388E-4</v>
       </c>
       <c r="M72" s="4">
@@ -4041,14 +4219,14 @@
         <v>80.968000000000004</v>
       </c>
       <c r="J73" s="7">
-        <f>G73*0.94-H73</f>
+        <f t="shared" si="2"/>
         <v>74.895399999999981</v>
       </c>
       <c r="K73" s="7">
         <v>74.896000000000001</v>
       </c>
       <c r="L73" s="7">
-        <f>J73-K73</f>
+        <f t="shared" si="3"/>
         <v>-6.0000000001991793E-4</v>
       </c>
       <c r="M73" s="4">
@@ -4084,14 +4262,14 @@
         <v>56.96</v>
       </c>
       <c r="J74" s="7">
-        <f>G74*0.94-H74</f>
+        <f t="shared" si="2"/>
         <v>52.687999999999995</v>
       </c>
       <c r="K74" s="7">
         <v>52.688000000000002</v>
       </c>
       <c r="L74" s="7">
-        <f>J74-K74</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="M74" s="4">
@@ -4127,14 +4305,14 @@
         <v>132.66399999999999</v>
       </c>
       <c r="J75" s="7">
-        <f>G75*0.94-H75</f>
+        <f t="shared" si="2"/>
         <v>122.71420000000001</v>
       </c>
       <c r="K75" s="7">
         <v>122.71599999999999</v>
       </c>
       <c r="L75" s="7">
-        <f>J75-K75</f>
+        <f t="shared" si="3"/>
         <v>-1.7999999999886995E-3</v>
       </c>
       <c r="M75" s="4">
@@ -4170,14 +4348,14 @@
         <v>94.215999999999994</v>
       </c>
       <c r="J76" s="7">
-        <f>G76*0.94-H76</f>
+        <f t="shared" si="2"/>
         <v>87.149799999999985</v>
       </c>
       <c r="K76" s="7">
         <v>87.156999999999996</v>
       </c>
       <c r="L76" s="7">
-        <f>J76-K76</f>
+        <f t="shared" si="3"/>
         <v>-7.2000000000116415E-3</v>
       </c>
       <c r="M76" s="4">
@@ -4213,11 +4391,11 @@
         <v>41.936</v>
       </c>
       <c r="J77" s="7">
-        <f>G77*0.94-H77</f>
+        <f t="shared" si="2"/>
         <v>38.790799999999997</v>
       </c>
       <c r="L77" s="7">
-        <f>J77-K77</f>
+        <f t="shared" si="3"/>
         <v>38.790799999999997</v>
       </c>
       <c r="M77" s="4"/>
@@ -4251,14 +4429,14 @@
         <v>37.896000000000001</v>
       </c>
       <c r="J78" s="7">
-        <f>G78*0.94-H78</f>
+        <f t="shared" si="2"/>
         <v>35.053799999999995</v>
       </c>
       <c r="K78" s="7">
         <v>35.052999999999997</v>
       </c>
       <c r="L78" s="7">
-        <f>J78-K78</f>
+        <f t="shared" si="3"/>
         <v>7.9999999999813554E-4</v>
       </c>
       <c r="M78" s="4">
@@ -4294,14 +4472,14 @@
         <v>30.103999999999999</v>
       </c>
       <c r="J79" s="7">
-        <f>G79*0.94-H79</f>
+        <f t="shared" si="2"/>
         <v>27.8462</v>
       </c>
       <c r="K79" s="7">
         <v>27.846</v>
       </c>
       <c r="L79" s="7">
-        <f>J79-K79</f>
+        <f t="shared" si="3"/>
         <v>1.9999999999953388E-4</v>
       </c>
       <c r="M79" s="4">
@@ -4337,14 +4515,14 @@
         <v>41.984000000000002</v>
       </c>
       <c r="J80" s="7">
-        <f>G80*0.94-H80</f>
+        <f t="shared" si="2"/>
         <v>38.835199999999993</v>
       </c>
       <c r="K80" s="7">
         <v>38.834000000000003</v>
       </c>
       <c r="L80" s="7">
-        <f>J80-K80</f>
+        <f t="shared" si="3"/>
         <v>1.1999999999900979E-3</v>
       </c>
       <c r="M80" s="4">
@@ -4380,11 +4558,11 @@
         <v>23.448</v>
       </c>
       <c r="J81" s="7">
-        <f>G81*0.94-H81</f>
+        <f t="shared" si="2"/>
         <v>21.689399999999999</v>
       </c>
       <c r="L81" s="7">
-        <f>J81-K81</f>
+        <f t="shared" si="3"/>
         <v>21.689399999999999</v>
       </c>
       <c r="M81" s="4"/>
@@ -4418,14 +4596,14 @@
         <v>88.96</v>
       </c>
       <c r="J82" s="7">
-        <f>G82*0.94-H82</f>
+        <f t="shared" si="2"/>
         <v>82.287999999999997</v>
       </c>
       <c r="K82" s="7">
         <v>82.287999999999997</v>
       </c>
       <c r="L82" s="7">
-        <f>J82-K82</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="M82" s="4">
@@ -4461,14 +4639,14 @@
         <v>2.024</v>
       </c>
       <c r="J83" s="7">
-        <f>G83*0.94-H83</f>
+        <f t="shared" si="2"/>
         <v>1.8721999999999996</v>
       </c>
       <c r="K83" s="7">
         <v>1.8720000000000001</v>
       </c>
       <c r="L83" s="7">
-        <f>J83-K83</f>
+        <f t="shared" si="3"/>
         <v>1.9999999999953388E-4</v>
       </c>
       <c r="M83" s="4">
@@ -4504,14 +4682,14 @@
         <v>81.695999999999998</v>
       </c>
       <c r="J84" s="7">
-        <f>G84*0.94-H84</f>
+        <f t="shared" si="2"/>
         <v>75.56880000000001</v>
       </c>
       <c r="K84" s="7">
         <v>75.569000000000003</v>
       </c>
       <c r="L84" s="7">
-        <f>J84-K84</f>
+        <f t="shared" si="3"/>
         <v>-1.9999999999242846E-4</v>
       </c>
       <c r="M84" s="4">
@@ -4547,14 +4725,14 @@
         <v>60.088000000000001</v>
       </c>
       <c r="J85" s="7">
-        <f>G85*0.94-H85</f>
+        <f t="shared" si="2"/>
         <v>55.581399999999995</v>
       </c>
       <c r="K85" s="7">
         <v>55.582999999999998</v>
       </c>
       <c r="L85" s="7">
-        <f>J85-K85</f>
+        <f t="shared" si="3"/>
         <v>-1.6000000000033765E-3</v>
       </c>
       <c r="M85" s="4">
@@ -4590,14 +4768,14 @@
         <v>188.768</v>
       </c>
       <c r="J86" s="7">
-        <f>G86*0.94-H86</f>
+        <f t="shared" si="2"/>
         <v>174.6104</v>
       </c>
       <c r="K86" s="7">
         <v>174.61099999999999</v>
       </c>
       <c r="L86" s="7">
-        <f>J86-K86</f>
+        <f t="shared" si="3"/>
         <v>-5.9999999999149622E-4</v>
       </c>
       <c r="M86" s="4">
@@ -4633,14 +4811,14 @@
         <v>26.327999999999999</v>
       </c>
       <c r="J87" s="7">
-        <f>G87*0.94-H87</f>
+        <f t="shared" si="2"/>
         <v>24.353399999999993</v>
       </c>
       <c r="K87" s="7">
         <v>24.353000000000002</v>
       </c>
       <c r="L87" s="7">
-        <f>J87-K87</f>
+        <f t="shared" si="3"/>
         <v>3.9999999999196234E-4</v>
       </c>
       <c r="M87" s="4">
@@ -4676,14 +4854,14 @@
         <v>39.887999999999998</v>
       </c>
       <c r="J88" s="7">
-        <f>G88*0.94-H88</f>
+        <f t="shared" si="2"/>
         <v>36.896399999999993</v>
       </c>
       <c r="K88" s="7">
         <v>36.896000000000001</v>
       </c>
       <c r="L88" s="7">
-        <f>J88-K88</f>
+        <f t="shared" si="3"/>
         <v>3.9999999999196234E-4</v>
       </c>
       <c r="M88" s="4">
@@ -4719,14 +4897,14 @@
         <v>93.415999999999997</v>
       </c>
       <c r="J89" s="7">
-        <f>G89*0.94-H89</f>
+        <f t="shared" si="2"/>
         <v>86.40979999999999</v>
       </c>
       <c r="K89" s="7">
         <v>86.41</v>
       </c>
       <c r="L89" s="7">
-        <f>J89-K89</f>
+        <f t="shared" si="3"/>
         <v>-2.0000000000663931E-4</v>
       </c>
       <c r="M89" s="4">
@@ -4762,14 +4940,14 @@
         <v>81.695999999999998</v>
       </c>
       <c r="J90" s="7">
-        <f>G90*0.94-H90</f>
+        <f t="shared" si="2"/>
         <v>75.56880000000001</v>
       </c>
       <c r="K90" s="7">
         <v>75.569000000000003</v>
       </c>
       <c r="L90" s="7">
-        <f>J90-K90</f>
+        <f t="shared" si="3"/>
         <v>-1.9999999999242846E-4</v>
       </c>
       <c r="M90" s="4">
@@ -4805,14 +4983,14 @@
         <v>56.68</v>
       </c>
       <c r="J91" s="7">
-        <f>G91*0.94-H91</f>
+        <f t="shared" si="2"/>
         <v>52.428999999999988</v>
       </c>
       <c r="K91" s="7">
         <v>54.006</v>
       </c>
       <c r="L91" s="7">
-        <f>J91-K91</f>
+        <f t="shared" si="3"/>
         <v>-1.5770000000000124</v>
       </c>
       <c r="M91" s="4">
@@ -4848,14 +5026,14 @@
         <v>134.52000000000001</v>
       </c>
       <c r="J92" s="7">
-        <f>G92*0.94-H92</f>
+        <f t="shared" si="2"/>
         <v>124.43100000000001</v>
       </c>
       <c r="K92" s="7">
         <v>124.432</v>
       </c>
       <c r="L92" s="7">
-        <f>J92-K92</f>
+        <f t="shared" si="3"/>
         <v>-9.9999999999056399E-4</v>
       </c>
       <c r="M92" s="4">
@@ -4891,14 +5069,14 @@
         <v>32</v>
       </c>
       <c r="J93" s="7">
-        <f>G93*0.94-H93</f>
+        <f t="shared" si="2"/>
         <v>29.599999999999994</v>
       </c>
       <c r="K93" s="7">
         <v>29.599</v>
       </c>
       <c r="L93" s="7">
-        <f>J93-K93</f>
+        <f t="shared" si="3"/>
         <v>9.9999999999411671E-4</v>
       </c>
       <c r="M93" s="4">
@@ -4934,14 +5112,14 @@
         <v>43.816000000000003</v>
       </c>
       <c r="J94" s="7">
-        <f>G94*0.94-H94</f>
+        <f t="shared" si="2"/>
         <v>40.529800000000002</v>
       </c>
       <c r="K94" s="7">
         <v>40.529000000000003</v>
       </c>
       <c r="L94" s="7">
-        <f>J94-K94</f>
+        <f t="shared" si="3"/>
         <v>7.9999999999813554E-4</v>
       </c>
       <c r="M94" s="4">
@@ -4977,14 +5155,14 @@
         <v>25.911999999999999</v>
       </c>
       <c r="J95" s="7">
-        <f>G95*0.94-H95</f>
+        <f t="shared" si="2"/>
         <v>23.968600000000002</v>
       </c>
       <c r="K95" s="7">
         <v>23.968</v>
       </c>
       <c r="L95" s="7">
-        <f>J95-K95</f>
+        <f t="shared" si="3"/>
         <v>6.0000000000215437E-4</v>
       </c>
       <c r="M95" s="4">
@@ -5020,14 +5198,14 @@
         <v>30.103999999999999</v>
       </c>
       <c r="J96" s="7">
-        <f>G96*0.94-H96</f>
+        <f t="shared" si="2"/>
         <v>27.8462</v>
       </c>
       <c r="K96" s="7">
         <v>27.846</v>
       </c>
       <c r="L96" s="7">
-        <f>J96-K96</f>
+        <f t="shared" si="3"/>
         <v>1.9999999999953388E-4</v>
       </c>
       <c r="M96" s="4">
@@ -5063,14 +5241,14 @@
         <v>93.415999999999997</v>
       </c>
       <c r="J97" s="7">
-        <f>G97*0.94-H97</f>
+        <f t="shared" si="2"/>
         <v>86.40979999999999</v>
       </c>
       <c r="K97" s="7">
         <v>86.41</v>
       </c>
       <c r="L97" s="7">
-        <f>J97-K97</f>
+        <f t="shared" si="3"/>
         <v>-2.0000000000663931E-4</v>
       </c>
       <c r="M97" s="4">
@@ -5106,14 +5284,14 @@
         <v>27.44</v>
       </c>
       <c r="J98" s="7">
-        <f>G98*0.94-H98</f>
+        <f t="shared" si="2"/>
         <v>25.381999999999998</v>
       </c>
       <c r="K98" s="7">
         <v>25.382000000000001</v>
       </c>
       <c r="L98" s="7">
-        <f>J98-K98</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="M98" s="4">
@@ -5149,14 +5327,14 @@
         <v>22.047999999999998</v>
       </c>
       <c r="J99" s="7">
-        <f>G99*0.94-H99</f>
+        <f t="shared" si="2"/>
         <v>20.394399999999997</v>
       </c>
       <c r="K99" s="7">
         <v>20.393999999999998</v>
       </c>
       <c r="L99" s="7">
-        <f>J99-K99</f>
+        <f t="shared" si="3"/>
         <v>3.9999999999906777E-4</v>
       </c>
       <c r="M99" s="4">
@@ -5192,14 +5370,14 @@
         <v>81.695999999999998</v>
       </c>
       <c r="J100" s="7">
-        <f>G100*0.94-H100</f>
+        <f t="shared" si="2"/>
         <v>75.56880000000001</v>
       </c>
       <c r="K100" s="7">
         <v>75.569000000000003</v>
       </c>
       <c r="L100" s="7">
-        <f>J100-K100</f>
+        <f t="shared" si="3"/>
         <v>-1.9999999999242846E-4</v>
       </c>
       <c r="M100" s="4">
@@ -5235,14 +5413,14 @@
         <v>58.384</v>
       </c>
       <c r="J101" s="7">
-        <f>G101*0.94-H101</f>
+        <f t="shared" si="2"/>
         <v>54.005200000000002</v>
       </c>
       <c r="K101" s="7">
         <v>54.006</v>
       </c>
       <c r="L101" s="7">
-        <f>J101-K101</f>
+        <f t="shared" si="3"/>
         <v>-7.9999999999813554E-4</v>
       </c>
       <c r="M101" s="4">
@@ -5278,14 +5456,14 @@
         <v>134.52000000000001</v>
       </c>
       <c r="J102" s="7">
-        <f>G102*0.94-H102</f>
+        <f t="shared" si="2"/>
         <v>124.43100000000001</v>
       </c>
       <c r="K102" s="7">
         <v>124.432</v>
       </c>
       <c r="L102" s="7">
-        <f>J102-K102</f>
+        <f t="shared" si="3"/>
         <v>-9.9999999999056399E-4</v>
       </c>
       <c r="M102" s="4">
@@ -5321,14 +5499,14 @@
         <v>28.192</v>
       </c>
       <c r="J103" s="7">
-        <f>G103*0.94-H103</f>
+        <f t="shared" si="2"/>
         <v>26.077599999999997</v>
       </c>
       <c r="K103" s="7">
         <v>26.077000000000002</v>
       </c>
       <c r="L103" s="7">
-        <f>J103-K103</f>
+        <f t="shared" si="3"/>
         <v>5.9999999999504894E-4</v>
       </c>
       <c r="M103" s="4">
@@ -5364,14 +5542,14 @@
         <v>25.96</v>
       </c>
       <c r="J104" s="7">
-        <f>G104*0.94-H104</f>
+        <f t="shared" si="2"/>
         <v>24.012999999999998</v>
       </c>
       <c r="K104" s="7">
         <v>24.013000000000002</v>
       </c>
       <c r="L104" s="7">
-        <f>J104-K104</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="M104" s="4">
@@ -5407,14 +5585,14 @@
         <v>30.103999999999999</v>
       </c>
       <c r="J105" s="7">
-        <f>G105*0.94-H105</f>
+        <f t="shared" si="2"/>
         <v>27.8462</v>
       </c>
       <c r="K105" s="7">
         <v>27.846</v>
       </c>
       <c r="L105" s="7">
-        <f>J105-K105</f>
+        <f t="shared" si="3"/>
         <v>1.9999999999953388E-4</v>
       </c>
       <c r="M105" s="4">
@@ -5450,14 +5628,14 @@
         <v>43.503999999999998</v>
       </c>
       <c r="J106" s="7">
-        <f>G106*0.94-H106</f>
+        <f t="shared" si="2"/>
         <v>40.241199999999999</v>
       </c>
       <c r="K106" s="7">
         <v>40.24</v>
       </c>
       <c r="L106" s="7">
-        <f>J106-K106</f>
+        <f t="shared" si="3"/>
         <v>1.1999999999972033E-3</v>
       </c>
       <c r="M106" s="4">
@@ -5493,14 +5671,14 @@
         <v>93.415999999999997</v>
       </c>
       <c r="J107" s="7">
-        <f>G107*0.94-H107</f>
+        <f t="shared" si="2"/>
         <v>86.40979999999999</v>
       </c>
       <c r="K107" s="7">
         <v>86.41</v>
       </c>
       <c r="L107" s="7">
-        <f>J107-K107</f>
+        <f t="shared" si="3"/>
         <v>-2.0000000000663931E-4</v>
       </c>
       <c r="M107" s="4">
@@ -5536,14 +5714,14 @@
         <v>58.384</v>
       </c>
       <c r="J108" s="7">
-        <f>G108*0.94-H108</f>
+        <f t="shared" si="2"/>
         <v>54.005200000000002</v>
       </c>
       <c r="K108" s="7">
         <v>54.006</v>
       </c>
       <c r="L108" s="7">
-        <f>J108-K108</f>
+        <f t="shared" si="3"/>
         <v>-7.9999999999813554E-4</v>
       </c>
       <c r="M108" s="4">
@@ -5579,14 +5757,14 @@
         <v>132.89599999999999</v>
       </c>
       <c r="J109" s="7">
-        <f>G109*0.94-H109</f>
+        <f t="shared" si="2"/>
         <v>122.9288</v>
       </c>
       <c r="K109" s="7">
         <v>122.93</v>
       </c>
       <c r="L109" s="7">
-        <f>J109-K109</f>
+        <f t="shared" si="3"/>
         <v>-1.2000000000114142E-3</v>
       </c>
       <c r="M109" s="4">
@@ -5622,14 +5800,14 @@
         <v>81.695999999999998</v>
       </c>
       <c r="J110" s="7">
-        <f>G110*0.94-H110</f>
+        <f t="shared" si="2"/>
         <v>75.56880000000001</v>
       </c>
       <c r="K110" s="7">
         <v>75.569000000000003</v>
       </c>
       <c r="L110" s="7">
-        <f>J110-K110</f>
+        <f t="shared" si="3"/>
         <v>-1.9999999999242846E-4</v>
       </c>
       <c r="M110" s="4">
@@ -5665,14 +5843,14 @@
         <v>17.256</v>
       </c>
       <c r="J111" s="7">
-        <f>G111*0.94-H111</f>
+        <f t="shared" si="2"/>
         <v>15.9618</v>
       </c>
       <c r="K111" s="7">
         <v>15.085000000000001</v>
       </c>
       <c r="L111" s="7">
-        <f>J111-K111</f>
+        <f t="shared" si="3"/>
         <v>0.87679999999999936</v>
       </c>
       <c r="M111" s="4">
@@ -5708,14 +5886,14 @@
         <v>29.504000000000001</v>
       </c>
       <c r="J112" s="7">
-        <f>G112*0.94-H112</f>
+        <f t="shared" si="2"/>
         <v>27.2912</v>
       </c>
       <c r="K112" s="7">
         <v>27.298999999999999</v>
       </c>
       <c r="L112" s="7">
-        <f>J112-K112</f>
+        <f t="shared" si="3"/>
         <v>-7.799999999999585E-3</v>
       </c>
       <c r="M112" s="4">
@@ -5751,14 +5929,14 @@
         <v>45.36</v>
       </c>
       <c r="J113" s="7">
-        <f>G113*0.94-H113</f>
+        <f t="shared" si="2"/>
         <v>41.957999999999998</v>
       </c>
       <c r="K113" s="7">
         <v>41.957000000000001</v>
       </c>
       <c r="L113" s="7">
-        <f>J113-K113</f>
+        <f t="shared" si="3"/>
         <v>9.9999999999766942E-4</v>
       </c>
       <c r="M113" s="4">
@@ -5794,14 +5972,14 @@
         <v>54.975999999999999</v>
       </c>
       <c r="J114" s="7">
-        <f>G114*0.94-H114</f>
+        <f t="shared" si="2"/>
         <v>50.852800000000002</v>
       </c>
       <c r="K114" s="7">
         <v>50.851999999999997</v>
       </c>
       <c r="L114" s="7">
-        <f>J114-K114</f>
+        <f t="shared" si="3"/>
         <v>8.0000000000524096E-4</v>
       </c>
       <c r="M114" s="4">
@@ -5837,14 +6015,14 @@
         <v>30.103999999999999</v>
       </c>
       <c r="J115" s="7">
-        <f>G115*0.94-H115</f>
+        <f t="shared" si="2"/>
         <v>27.8462</v>
       </c>
       <c r="K115" s="7">
         <v>27.846</v>
       </c>
       <c r="L115" s="7">
-        <f>J115-K115</f>
+        <f t="shared" si="3"/>
         <v>1.9999999999953388E-4</v>
       </c>
       <c r="M115" s="4">
@@ -5880,14 +6058,14 @@
         <v>45.527999999999999</v>
       </c>
       <c r="J116" s="7">
-        <f>G116*0.94-H116</f>
+        <f t="shared" si="2"/>
         <v>42.113399999999999</v>
       </c>
       <c r="K116" s="7">
         <v>42.113</v>
       </c>
       <c r="L116" s="7">
-        <f>J116-K116</f>
+        <f t="shared" si="3"/>
         <v>3.9999999999906777E-4</v>
       </c>
       <c r="M116" s="4">
@@ -5923,14 +6101,14 @@
         <v>58.384</v>
       </c>
       <c r="J117" s="7">
-        <f>G117*0.94-H117</f>
+        <f t="shared" si="2"/>
         <v>54.005200000000002</v>
       </c>
       <c r="K117" s="7">
         <v>54.006</v>
       </c>
       <c r="L117" s="7">
-        <f>J117-K117</f>
+        <f t="shared" si="3"/>
         <v>-7.9999999999813554E-4</v>
       </c>
       <c r="M117" s="4">
@@ -5966,14 +6144,14 @@
         <v>134.52000000000001</v>
       </c>
       <c r="J118" s="7">
-        <f>G118*0.94-H118</f>
+        <f t="shared" si="2"/>
         <v>124.43100000000001</v>
       </c>
       <c r="K118" s="7">
         <v>124.432</v>
       </c>
       <c r="L118" s="7">
-        <f>J118-K118</f>
+        <f t="shared" si="3"/>
         <v>-9.9999999999056399E-4</v>
       </c>
       <c r="M118" s="4">
@@ -6009,14 +6187,14 @@
         <v>81.695999999999998</v>
       </c>
       <c r="J119" s="7">
-        <f>G119*0.94-H119</f>
+        <f t="shared" si="2"/>
         <v>75.56880000000001</v>
       </c>
       <c r="K119" s="7">
         <v>75.569000000000003</v>
       </c>
       <c r="L119" s="7">
-        <f>J119-K119</f>
+        <f t="shared" si="3"/>
         <v>-1.9999999999242846E-4</v>
       </c>
       <c r="M119" s="4">
@@ -6052,14 +6230,14 @@
         <v>47.984000000000002</v>
       </c>
       <c r="J120" s="7">
-        <f>G120*0.94-H120</f>
+        <f t="shared" si="2"/>
         <v>44.38519999999999</v>
       </c>
       <c r="K120" s="7">
         <v>44.386000000000003</v>
       </c>
       <c r="L120" s="7">
-        <f>J120-K120</f>
+        <f t="shared" si="3"/>
         <v>-8.0000000001234639E-4</v>
       </c>
       <c r="M120" s="4">
@@ -6095,14 +6273,14 @@
         <v>23.896000000000001</v>
       </c>
       <c r="J121" s="7">
-        <f>G121*0.94-H121</f>
+        <f t="shared" si="2"/>
         <v>22.1038</v>
       </c>
       <c r="K121" s="7">
         <v>22.103999999999999</v>
       </c>
       <c r="L121" s="7">
-        <f>J121-K121</f>
+        <f t="shared" si="3"/>
         <v>-1.9999999999953388E-4</v>
       </c>
       <c r="M121" s="4">
@@ -6138,14 +6316,14 @@
         <v>30.591999999999999</v>
       </c>
       <c r="J122" s="7">
-        <f>G122*0.94-H122</f>
+        <f t="shared" si="2"/>
         <v>28.297599999999999</v>
       </c>
       <c r="K122" s="7">
         <v>28.297999999999998</v>
       </c>
       <c r="L122" s="7">
-        <f>J122-K122</f>
+        <f t="shared" si="3"/>
         <v>-3.9999999999906777E-4</v>
       </c>
       <c r="M122" s="4">
@@ -6181,14 +6359,14 @@
         <v>35.872</v>
       </c>
       <c r="J123" s="7">
-        <f>G123*0.94-H123</f>
+        <f t="shared" si="2"/>
         <v>33.181600000000003</v>
       </c>
       <c r="K123" s="7">
         <v>33.182000000000002</v>
       </c>
       <c r="L123" s="7">
-        <f>J123-K123</f>
+        <f t="shared" si="3"/>
         <v>-3.9999999999906777E-4</v>
       </c>
       <c r="M123" s="4">
@@ -6224,14 +6402,14 @@
         <v>94.512</v>
       </c>
       <c r="J124" s="7">
-        <f>G124*0.94-H124</f>
+        <f t="shared" si="2"/>
         <v>87.423599999999993</v>
       </c>
       <c r="K124" s="7">
         <v>87.426000000000002</v>
       </c>
       <c r="L124" s="7">
-        <f>J124-K124</f>
+        <f t="shared" si="3"/>
         <v>-2.4000000000086175E-3</v>
       </c>
       <c r="M124" s="4">
@@ -6267,14 +6445,14 @@
         <v>164.15199999999999</v>
       </c>
       <c r="J125" s="7">
-        <f>G125*0.94-H125</f>
+        <f t="shared" si="2"/>
         <v>151.84059999999999</v>
       </c>
       <c r="K125" s="7">
         <v>151.84100000000001</v>
       </c>
       <c r="L125" s="7">
-        <f>J125-K125</f>
+        <f t="shared" si="3"/>
         <v>-4.0000000001327862E-4</v>
       </c>
       <c r="M125" s="4">
@@ -6310,14 +6488,14 @@
         <v>42.264000000000003</v>
       </c>
       <c r="J126" s="7">
-        <f>G126*0.94-H126</f>
+        <f t="shared" si="2"/>
         <v>39.094199999999994</v>
       </c>
       <c r="K126" s="7">
         <v>39.094999999999999</v>
       </c>
       <c r="L126" s="7">
-        <f>J126-K126</f>
+        <f t="shared" si="3"/>
         <v>-8.0000000000524096E-4</v>
       </c>
       <c r="M126" s="4">
@@ -6353,14 +6531,14 @@
         <v>30.111999999999998</v>
       </c>
       <c r="J127" s="7">
-        <f>G127*0.94-H127</f>
+        <f t="shared" si="2"/>
         <v>27.8536</v>
       </c>
       <c r="K127" s="7">
         <v>27.853000000000002</v>
       </c>
       <c r="L127" s="7">
-        <f>J127-K127</f>
+        <f t="shared" si="3"/>
         <v>5.9999999999860165E-4</v>
       </c>
       <c r="M127" s="4">
@@ -6396,14 +6574,14 @@
         <v>100.47199999999999</v>
       </c>
       <c r="J128" s="7">
-        <f>G128*0.94-H128</f>
+        <f t="shared" si="2"/>
         <v>92.936599999999999</v>
       </c>
       <c r="K128" s="7">
         <v>92.936999999999998</v>
       </c>
       <c r="L128" s="7">
-        <f>J128-K128</f>
+        <f t="shared" si="3"/>
         <v>-3.9999999999906777E-4</v>
       </c>
       <c r="M128" s="4">
@@ -6439,14 +6617,14 @@
         <v>9.68</v>
       </c>
       <c r="J129" s="7">
-        <f>G129*0.94-H129</f>
+        <f t="shared" si="2"/>
         <v>8.9539999999999988</v>
       </c>
       <c r="K129" s="7">
         <v>8.9540000000000006</v>
       </c>
       <c r="L129" s="7">
-        <f>J129-K129</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="M129" s="4">
@@ -6482,14 +6660,14 @@
         <v>192.40799999999999</v>
       </c>
       <c r="J130" s="7">
-        <f>G130*0.94-H130</f>
+        <f t="shared" ref="J130:J193" si="4">G130*0.94-H130</f>
         <v>177.97739999999999</v>
       </c>
       <c r="K130" s="7">
         <v>177.97800000000001</v>
       </c>
       <c r="L130" s="7">
-        <f>J130-K130</f>
+        <f t="shared" ref="L130:L193" si="5">J130-K130</f>
         <v>-6.0000000001991793E-4</v>
       </c>
       <c r="M130" s="4">
@@ -6525,14 +6703,14 @@
         <v>36.216000000000001</v>
       </c>
       <c r="J131" s="7">
-        <f>G131*0.94-H131</f>
+        <f t="shared" si="4"/>
         <v>33.4998</v>
       </c>
       <c r="K131" s="7">
         <v>33.5</v>
       </c>
       <c r="L131" s="7">
-        <f>J131-K131</f>
+        <f t="shared" si="5"/>
         <v>-1.9999999999953388E-4</v>
       </c>
       <c r="M131" s="4">
@@ -6568,14 +6746,14 @@
         <v>103.872</v>
       </c>
       <c r="J132" s="7">
-        <f>G132*0.94-H132</f>
+        <f t="shared" si="4"/>
         <v>96.081599999999995</v>
       </c>
       <c r="K132" s="7">
         <v>96.084000000000003</v>
       </c>
       <c r="L132" s="7">
-        <f>J132-K132</f>
+        <f t="shared" si="5"/>
         <v>-2.4000000000086175E-3</v>
       </c>
       <c r="M132" s="4">
@@ -6611,11 +6789,11 @@
         <v>43.808</v>
       </c>
       <c r="J133" s="7">
-        <f>G133*0.94-H133</f>
+        <f t="shared" si="4"/>
         <v>40.522399999999998</v>
       </c>
       <c r="L133" s="7">
-        <f>J133-K133</f>
+        <f t="shared" si="5"/>
         <v>40.522399999999998</v>
       </c>
       <c r="M133" s="4"/>
@@ -6649,11 +6827,11 @@
         <v>30.103999999999999</v>
       </c>
       <c r="J134" s="7">
-        <f>G134*0.94-H134</f>
+        <f t="shared" si="4"/>
         <v>27.8462</v>
       </c>
       <c r="L134" s="7">
-        <f>J134-K134</f>
+        <f t="shared" si="5"/>
         <v>27.8462</v>
       </c>
       <c r="M134" s="4"/>
@@ -6687,11 +6865,11 @@
         <v>93.415999999999997</v>
       </c>
       <c r="J135" s="7">
-        <f>G135*0.94-H135</f>
+        <f t="shared" si="4"/>
         <v>86.40979999999999</v>
       </c>
       <c r="L135" s="7">
-        <f>J135-K135</f>
+        <f t="shared" si="5"/>
         <v>86.40979999999999</v>
       </c>
       <c r="M135" s="4"/>
@@ -6725,11 +6903,11 @@
         <v>15.256</v>
       </c>
       <c r="J136" s="7">
-        <f>G136*0.94-H136</f>
+        <f t="shared" si="4"/>
         <v>14.111799999999999</v>
       </c>
       <c r="L136" s="7">
-        <f>J136-K136</f>
+        <f t="shared" si="5"/>
         <v>14.111799999999999</v>
       </c>
       <c r="M136" s="4"/>
@@ -6763,14 +6941,14 @@
         <v>94.512</v>
       </c>
       <c r="J137" s="7">
-        <f>G137*0.94-H137</f>
+        <f t="shared" si="4"/>
         <v>87.423599999999993</v>
       </c>
       <c r="K137" s="7">
         <v>87.426000000000002</v>
       </c>
       <c r="L137" s="7">
-        <f>J137-K137</f>
+        <f t="shared" si="5"/>
         <v>-2.4000000000086175E-3</v>
       </c>
       <c r="M137" s="4">
@@ -6806,14 +6984,14 @@
         <v>35.872</v>
       </c>
       <c r="J138" s="7">
-        <f>G138*0.94-H138</f>
+        <f t="shared" si="4"/>
         <v>33.181600000000003</v>
       </c>
       <c r="K138" s="7">
         <v>33.182000000000002</v>
       </c>
       <c r="L138" s="7">
-        <f>J138-K138</f>
+        <f t="shared" si="5"/>
         <v>-3.9999999999906777E-4</v>
       </c>
       <c r="M138" s="4">
@@ -6849,14 +7027,14 @@
         <v>155.80799999999999</v>
       </c>
       <c r="J139" s="7">
-        <f>G139*0.94-H139</f>
+        <f t="shared" si="4"/>
         <v>144.12239999999997</v>
       </c>
       <c r="K139" s="7">
         <v>144.12299999999999</v>
       </c>
       <c r="L139" s="7">
-        <f>J139-K139</f>
+        <f t="shared" si="5"/>
         <v>-6.0000000001991793E-4</v>
       </c>
       <c r="M139" s="4">
@@ -6892,14 +7070,14 @@
         <v>47.984000000000002</v>
       </c>
       <c r="J140" s="7">
-        <f>G140*0.94-H140</f>
+        <f t="shared" si="4"/>
         <v>44.38519999999999</v>
       </c>
       <c r="K140" s="7">
         <v>44.386000000000003</v>
       </c>
       <c r="L140" s="7">
-        <f>J140-K140</f>
+        <f t="shared" si="5"/>
         <v>-8.0000000001234639E-4</v>
       </c>
       <c r="M140" s="4">
@@ -6935,14 +7113,14 @@
         <v>74.536000000000001</v>
       </c>
       <c r="J141" s="7">
-        <f>G141*0.94-H141</f>
+        <f t="shared" si="4"/>
         <v>68.945799999999991</v>
       </c>
       <c r="K141" s="7">
         <v>68.945999999999998</v>
       </c>
       <c r="L141" s="7">
-        <f>J141-K141</f>
+        <f t="shared" si="5"/>
         <v>-2.0000000000663931E-4</v>
       </c>
       <c r="M141" s="4">
@@ -6978,14 +7156,14 @@
         <v>154.136</v>
       </c>
       <c r="J142" s="7">
-        <f>G142*0.94-H142</f>
+        <f t="shared" si="4"/>
         <v>142.57579999999999</v>
       </c>
       <c r="K142" s="7">
         <v>142.577</v>
       </c>
       <c r="L142" s="7">
-        <f>J142-K142</f>
+        <f t="shared" si="5"/>
         <v>-1.2000000000114142E-3</v>
       </c>
       <c r="M142" s="4">
@@ -7021,14 +7199,14 @@
         <v>42.264000000000003</v>
       </c>
       <c r="J143" s="7">
-        <f>G143*0.94-H143</f>
+        <f t="shared" si="4"/>
         <v>39.094199999999994</v>
       </c>
       <c r="K143" s="7">
         <v>39.094999999999999</v>
       </c>
       <c r="L143" s="7">
-        <f>J143-K143</f>
+        <f t="shared" si="5"/>
         <v>-8.0000000000524096E-4</v>
       </c>
       <c r="M143" s="4">
@@ -7064,14 +7242,14 @@
         <v>9.68</v>
       </c>
       <c r="J144" s="7">
-        <f>G144*0.94-H144</f>
+        <f t="shared" si="4"/>
         <v>8.9539999999999988</v>
       </c>
       <c r="K144" s="7">
         <v>8.9540000000000006</v>
       </c>
       <c r="L144" s="7">
-        <f>J144-K144</f>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="M144" s="4">
@@ -7107,14 +7285,14 @@
         <v>30.591999999999999</v>
       </c>
       <c r="J145" s="7">
-        <f>G145*0.94-H145</f>
+        <f t="shared" si="4"/>
         <v>28.297599999999999</v>
       </c>
       <c r="K145" s="7">
         <v>28.297999999999998</v>
       </c>
       <c r="L145" s="7">
-        <f>J145-K145</f>
+        <f t="shared" si="5"/>
         <v>-3.9999999999906777E-4</v>
       </c>
       <c r="M145" s="4">
@@ -7150,14 +7328,14 @@
         <v>20.143999999999998</v>
       </c>
       <c r="J146" s="7">
-        <f>G146*0.94-H146</f>
+        <f t="shared" si="4"/>
         <v>18.633200000000002</v>
       </c>
       <c r="K146" s="7">
         <v>18.634</v>
       </c>
       <c r="L146" s="7">
-        <f>J146-K146</f>
+        <f t="shared" si="5"/>
         <v>-7.9999999999813554E-4</v>
       </c>
       <c r="M146" s="4">
@@ -7193,14 +7371,14 @@
         <v>36.216000000000001</v>
       </c>
       <c r="J147" s="7">
-        <f>G147*0.94-H147</f>
+        <f t="shared" si="4"/>
         <v>33.4998</v>
       </c>
       <c r="K147" s="7">
         <v>33.5</v>
       </c>
       <c r="L147" s="7">
-        <f>J147-K147</f>
+        <f t="shared" si="5"/>
         <v>-1.9999999999953388E-4</v>
       </c>
       <c r="M147" s="4">
@@ -7236,14 +7414,14 @@
         <v>23.896000000000001</v>
       </c>
       <c r="J148" s="7">
-        <f>G148*0.94-H148</f>
+        <f t="shared" si="4"/>
         <v>22.1038</v>
       </c>
       <c r="K148" s="7">
         <v>22.103999999999999</v>
       </c>
       <c r="L148" s="7">
-        <f>J148-K148</f>
+        <f t="shared" si="5"/>
         <v>-1.9999999999953388E-4</v>
       </c>
       <c r="M148" s="4">
@@ -7279,11 +7457,11 @@
         <v>81.695999999999998</v>
       </c>
       <c r="J149" s="7">
-        <f>G149*0.94-H149</f>
+        <f t="shared" si="4"/>
         <v>75.56880000000001</v>
       </c>
       <c r="L149" s="7">
-        <f>J149-K149</f>
+        <f t="shared" si="5"/>
         <v>75.56880000000001</v>
       </c>
       <c r="M149" s="4"/>
@@ -7317,11 +7495,11 @@
         <v>134.52000000000001</v>
       </c>
       <c r="J150" s="7">
-        <f>G150*0.94-H150</f>
+        <f t="shared" si="4"/>
         <v>124.43100000000001</v>
       </c>
       <c r="L150" s="7">
-        <f>J150-K150</f>
+        <f t="shared" si="5"/>
         <v>124.43100000000001</v>
       </c>
       <c r="M150" s="4"/>
@@ -7355,11 +7533,11 @@
         <v>58.384</v>
       </c>
       <c r="J151" s="7">
-        <f>G151*0.94-H151</f>
+        <f t="shared" si="4"/>
         <v>54.005200000000002</v>
       </c>
       <c r="L151" s="7">
-        <f>J151-K151</f>
+        <f t="shared" si="5"/>
         <v>54.005200000000002</v>
       </c>
       <c r="M151" s="4"/>
@@ -7393,11 +7571,11 @@
         <v>30.984000000000002</v>
       </c>
       <c r="J152" s="7">
-        <f>G152*0.94-H152</f>
+        <f t="shared" si="4"/>
         <v>28.660199999999996</v>
       </c>
       <c r="L152" s="7">
-        <f>J152-K152</f>
+        <f t="shared" si="5"/>
         <v>28.660199999999996</v>
       </c>
       <c r="M152" s="4"/>
@@ -7431,14 +7609,14 @@
         <v>38.456000000000003</v>
       </c>
       <c r="J153" s="7">
-        <f>G153*0.94-H153</f>
+        <f t="shared" si="4"/>
         <v>35.571799999999996</v>
       </c>
       <c r="K153" s="7">
         <v>35.570999999999998</v>
       </c>
       <c r="L153" s="7">
-        <f>J153-K153</f>
+        <f t="shared" si="5"/>
         <v>7.9999999999813554E-4</v>
       </c>
       <c r="M153" s="4">
@@ -7474,14 +7652,14 @@
         <v>30.808</v>
       </c>
       <c r="J154" s="7">
-        <f>G154*0.94-H154</f>
+        <f t="shared" si="4"/>
         <v>28.497399999999999</v>
       </c>
       <c r="K154" s="6">
         <v>28.497</v>
       </c>
       <c r="L154" s="7">
-        <f>J154-K154</f>
+        <f t="shared" si="5"/>
         <v>3.9999999999906777E-4</v>
       </c>
       <c r="M154" s="4">
@@ -7517,11 +7695,11 @@
         <v>33.231999999999999</v>
       </c>
       <c r="J155" s="7">
-        <f>G155*0.94-H155</f>
+        <f t="shared" si="4"/>
         <v>30.739599999999996</v>
       </c>
       <c r="L155" s="7">
-        <f>J155-K155</f>
+        <f t="shared" si="5"/>
         <v>30.739599999999996</v>
       </c>
       <c r="M155" s="4"/>
@@ -7555,11 +7733,11 @@
         <v>19.655999999999999</v>
       </c>
       <c r="J156" s="7">
-        <f>G156*0.94-H156</f>
+        <f t="shared" si="4"/>
         <v>18.181800000000003</v>
       </c>
       <c r="L156" s="7">
-        <f>J156-K156</f>
+        <f t="shared" si="5"/>
         <v>18.181800000000003</v>
       </c>
       <c r="M156" s="4"/>
@@ -7593,14 +7771,14 @@
         <v>42.776000000000003</v>
       </c>
       <c r="J157" s="7">
-        <f>G157*0.94-H157</f>
+        <f t="shared" si="4"/>
         <v>39.567799999999991</v>
       </c>
       <c r="K157" s="7">
         <v>39.567</v>
       </c>
       <c r="L157" s="7">
-        <f>J157-K157</f>
+        <f t="shared" si="5"/>
         <v>7.9999999999103011E-4</v>
       </c>
       <c r="M157" s="4">
@@ -7636,14 +7814,14 @@
         <v>40.119999999999997</v>
       </c>
       <c r="J158" s="7">
-        <f>G158*0.94-H158</f>
+        <f t="shared" si="4"/>
         <v>37.110999999999997</v>
       </c>
       <c r="K158" s="7">
         <v>37.11</v>
       </c>
       <c r="L158" s="7">
-        <f>J158-K158</f>
+        <f t="shared" si="5"/>
         <v>9.9999999999766942E-4</v>
       </c>
       <c r="M158" s="4">
@@ -7679,11 +7857,11 @@
         <v>110.24</v>
       </c>
       <c r="J159" s="7">
-        <f>G159*0.94-H159</f>
+        <f t="shared" si="4"/>
         <v>101.97200000000001</v>
       </c>
       <c r="L159" s="7">
-        <f>J159-K159</f>
+        <f t="shared" si="5"/>
         <v>101.97200000000001</v>
       </c>
       <c r="M159" s="4"/>
@@ -7717,11 +7895,11 @@
         <v>21.975999999999999</v>
       </c>
       <c r="J160" s="7">
-        <f>G160*0.94-H160</f>
+        <f t="shared" si="4"/>
         <v>20.327799999999996</v>
       </c>
       <c r="L160" s="7">
-        <f>J160-K160</f>
+        <f t="shared" si="5"/>
         <v>20.327799999999996</v>
       </c>
       <c r="M160" s="4"/>
@@ -7755,11 +7933,11 @@
         <v>37.103999999999999</v>
       </c>
       <c r="J161" s="7">
-        <f>G161*0.94-H161</f>
+        <f t="shared" si="4"/>
         <v>34.321200000000005</v>
       </c>
       <c r="L161" s="7">
-        <f>J161-K161</f>
+        <f t="shared" si="5"/>
         <v>34.321200000000005</v>
       </c>
       <c r="M161" s="4"/>
@@ -7793,11 +7971,11 @@
         <v>31.103999999999999</v>
       </c>
       <c r="J162" s="7">
-        <f>G162*0.94-H162</f>
+        <f t="shared" si="4"/>
         <v>28.771200000000004</v>
       </c>
       <c r="L162" s="7">
-        <f>J162-K162</f>
+        <f t="shared" si="5"/>
         <v>28.771200000000004</v>
       </c>
       <c r="M162" s="4"/>
@@ -7831,11 +8009,11 @@
         <v>21.8</v>
       </c>
       <c r="J163" s="7">
-        <f>G163*0.94-H163</f>
+        <f t="shared" si="4"/>
         <v>20.164999999999999</v>
       </c>
       <c r="L163" s="7">
-        <f>J163-K163</f>
+        <f t="shared" si="5"/>
         <v>20.164999999999999</v>
       </c>
       <c r="M163" s="4"/>
@@ -7869,14 +8047,14 @@
         <v>39.183999999999997</v>
       </c>
       <c r="J164" s="7">
-        <f>G164*0.94-H164</f>
+        <f t="shared" si="4"/>
         <v>36.245199999999997</v>
       </c>
       <c r="K164" s="7">
         <v>36.244</v>
       </c>
       <c r="L164" s="7">
-        <f>J164-K164</f>
+        <f t="shared" si="5"/>
         <v>1.1999999999972033E-3</v>
       </c>
       <c r="M164" s="4">
@@ -7912,14 +8090,14 @@
         <v>33.472000000000001</v>
       </c>
       <c r="J165" s="7">
-        <f>G165*0.94-H165</f>
+        <f t="shared" si="4"/>
         <v>30.961599999999997</v>
       </c>
       <c r="K165" s="7">
         <v>30.960999999999999</v>
       </c>
       <c r="L165" s="7">
-        <f>J165-K165</f>
+        <f t="shared" si="5"/>
         <v>5.9999999999860165E-4</v>
       </c>
       <c r="M165" s="4">
@@ -7955,11 +8133,11 @@
         <v>48.552</v>
       </c>
       <c r="J166" s="7">
-        <f>G166*0.94-H166</f>
+        <f t="shared" si="4"/>
         <v>44.910599999999995</v>
       </c>
       <c r="L166" s="7">
-        <f>J166-K166</f>
+        <f t="shared" si="5"/>
         <v>44.910599999999995</v>
       </c>
       <c r="M166" s="4"/>
@@ -7993,14 +8171,14 @@
         <v>127.80800000000001</v>
       </c>
       <c r="J167" s="7">
-        <f>G167*0.94-H167</f>
+        <f t="shared" si="4"/>
         <v>118.22239999999999</v>
       </c>
       <c r="K167" s="7">
         <v>118.224</v>
       </c>
       <c r="L167" s="7">
-        <f>J167-K167</f>
+        <f t="shared" si="5"/>
         <v>-1.6000000000104819E-3</v>
       </c>
       <c r="M167" s="4">
@@ -8036,14 +8214,14 @@
         <v>35.872</v>
       </c>
       <c r="J168" s="7">
-        <f>G168*0.94-H168</f>
+        <f t="shared" si="4"/>
         <v>33.181600000000003</v>
       </c>
       <c r="K168" s="7">
         <v>33.182000000000002</v>
       </c>
       <c r="L168" s="7">
-        <f>J168-K168</f>
+        <f t="shared" si="5"/>
         <v>-3.9999999999906777E-4</v>
       </c>
       <c r="M168" s="4">
@@ -8079,14 +8257,14 @@
         <v>25.463999999999999</v>
       </c>
       <c r="J169" s="7">
-        <f>G169*0.94-H169</f>
+        <f t="shared" si="4"/>
         <v>23.554199999999998</v>
       </c>
       <c r="K169" s="7">
         <v>23.553999999999998</v>
       </c>
       <c r="L169" s="7">
-        <f>J169-K169</f>
+        <f t="shared" si="5"/>
         <v>1.9999999999953388E-4</v>
       </c>
       <c r="M169" s="4">
@@ -8122,14 +8300,14 @@
         <v>45.847999999999999</v>
       </c>
       <c r="J170" s="7">
-        <f>G170*0.94-H170</f>
+        <f t="shared" si="4"/>
         <v>42.409400000000005</v>
       </c>
       <c r="K170" s="7">
         <v>42.408999999999999</v>
       </c>
       <c r="L170" s="7">
-        <f>J170-K170</f>
+        <f t="shared" si="5"/>
         <v>4.000000000061732E-4</v>
       </c>
       <c r="M170" s="4">
@@ -8165,14 +8343,14 @@
         <v>32.264000000000003</v>
       </c>
       <c r="J171" s="7">
-        <f>G171*0.94-H171</f>
+        <f t="shared" si="4"/>
         <v>29.844199999999994</v>
       </c>
       <c r="K171" s="7">
         <v>29.843</v>
       </c>
       <c r="L171" s="7">
-        <f>J171-K171</f>
+        <f t="shared" si="5"/>
         <v>1.1999999999936506E-3</v>
       </c>
       <c r="M171" s="4">
@@ -8208,11 +8386,11 @@
         <v>43.503999999999998</v>
       </c>
       <c r="J172" s="7">
-        <f>G172*0.94-H172</f>
+        <f t="shared" si="4"/>
         <v>40.241199999999999</v>
       </c>
       <c r="L172" s="7">
-        <f>J172-K172</f>
+        <f t="shared" si="5"/>
         <v>40.241199999999999</v>
       </c>
       <c r="M172" s="4"/>
@@ -8246,11 +8424,11 @@
         <v>34.735999999999997</v>
       </c>
       <c r="J173" s="7">
-        <f>G173*0.94-H173</f>
+        <f t="shared" si="4"/>
         <v>32.130800000000001</v>
       </c>
       <c r="L173" s="7">
-        <f>J173-K173</f>
+        <f t="shared" si="5"/>
         <v>32.130800000000001</v>
       </c>
       <c r="M173" s="4"/>
@@ -8284,11 +8462,11 @@
         <v>47.863999999999997</v>
       </c>
       <c r="J174" s="7">
-        <f>G174*0.94-H174</f>
+        <f t="shared" si="4"/>
         <v>44.274199999999993</v>
       </c>
       <c r="L174" s="7">
-        <f>J174-K174</f>
+        <f t="shared" si="5"/>
         <v>44.274199999999993</v>
       </c>
       <c r="M174" s="4"/>
@@ -8322,14 +8500,14 @@
         <v>182.65600000000001</v>
       </c>
       <c r="J175" s="7">
-        <f>G175*0.94-H175</f>
+        <f t="shared" si="4"/>
         <v>168.95679999999999</v>
       </c>
       <c r="K175" s="7">
         <v>168.95699999999999</v>
       </c>
       <c r="L175" s="7">
-        <f>J175-K175</f>
+        <f t="shared" si="5"/>
         <v>-2.0000000000663931E-4</v>
       </c>
       <c r="M175" s="4">
@@ -8365,14 +8543,14 @@
         <v>58.136000000000003</v>
       </c>
       <c r="J176" s="7">
-        <f>G176*0.94-H176</f>
+        <f t="shared" si="4"/>
         <v>53.775799999999997</v>
       </c>
       <c r="K176" s="7">
         <v>53.777000000000001</v>
       </c>
       <c r="L176" s="7">
-        <f>J176-K176</f>
+        <f t="shared" si="5"/>
         <v>-1.2000000000043087E-3</v>
       </c>
       <c r="M176" s="4">
@@ -8408,14 +8586,14 @@
         <v>100.47199999999999</v>
       </c>
       <c r="J177" s="7">
-        <f>G177*0.94-H177</f>
+        <f t="shared" si="4"/>
         <v>92.936599999999999</v>
       </c>
       <c r="K177" s="7">
         <v>92.936999999999998</v>
       </c>
       <c r="L177" s="7">
-        <f>J177-K177</f>
+        <f t="shared" si="5"/>
         <v>-3.9999999999906777E-4</v>
       </c>
       <c r="M177" s="4">
@@ -8451,14 +8629,14 @@
         <v>154.136</v>
       </c>
       <c r="J178" s="7">
-        <f>G178*0.94-H178</f>
+        <f t="shared" si="4"/>
         <v>142.57579999999999</v>
       </c>
       <c r="K178" s="7">
         <v>142.577</v>
       </c>
       <c r="L178" s="7">
-        <f>J178-K178</f>
+        <f t="shared" si="5"/>
         <v>-1.2000000000114142E-3</v>
       </c>
       <c r="M178" s="4">
@@ -8494,14 +8672,14 @@
         <v>57.552</v>
       </c>
       <c r="J179" s="7">
-        <f>G179*0.94-H179</f>
+        <f t="shared" si="4"/>
         <v>53.235599999999998</v>
       </c>
       <c r="K179" s="7">
         <v>53.235999999999997</v>
       </c>
       <c r="L179" s="7">
-        <f>J179-K179</f>
+        <f t="shared" si="5"/>
         <v>-3.9999999999906777E-4</v>
       </c>
       <c r="M179" s="4">
@@ -8537,14 +8715,14 @@
         <v>71.328000000000003</v>
       </c>
       <c r="J180" s="7">
-        <f>G180*0.94-H180</f>
+        <f t="shared" si="4"/>
         <v>65.978399999999993</v>
       </c>
       <c r="K180" s="7">
         <v>65.978999999999999</v>
       </c>
       <c r="L180" s="7">
-        <f>J180-K180</f>
+        <f t="shared" si="5"/>
         <v>-6.0000000000570708E-4</v>
       </c>
       <c r="M180" s="4">
@@ -8580,14 +8758,14 @@
         <v>33.536000000000001</v>
       </c>
       <c r="J181" s="7">
-        <f>G181*0.94-H181</f>
+        <f t="shared" si="4"/>
         <v>31.020800000000001</v>
       </c>
       <c r="K181" s="7">
         <v>31.021000000000001</v>
       </c>
       <c r="L181" s="7">
-        <f>J181-K181</f>
+        <f t="shared" si="5"/>
         <v>-1.9999999999953388E-4</v>
       </c>
       <c r="M181" s="4">
@@ -8623,14 +8801,14 @@
         <v>37.847999999999999</v>
       </c>
       <c r="J182" s="7">
-        <f>G182*0.94-H182</f>
+        <f t="shared" si="4"/>
         <v>35.009399999999999</v>
       </c>
       <c r="K182" s="7">
         <v>35.01</v>
       </c>
       <c r="L182" s="7">
-        <f>J182-K182</f>
+        <f t="shared" si="5"/>
         <v>-5.9999999999860165E-4</v>
       </c>
       <c r="M182" s="4">
@@ -8666,11 +8844,11 @@
         <v>198.08</v>
       </c>
       <c r="J183" s="7">
-        <f>G183*0.94-H183</f>
+        <f t="shared" si="4"/>
         <v>183.22399999999996</v>
       </c>
       <c r="L183" s="7">
-        <f>J183-K183</f>
+        <f t="shared" si="5"/>
         <v>183.22399999999996</v>
       </c>
       <c r="M183" s="4"/>
@@ -8704,11 +8882,11 @@
         <v>119.024</v>
       </c>
       <c r="J184" s="7">
-        <f>G184*0.94-H184</f>
+        <f t="shared" si="4"/>
         <v>110.09719999999999</v>
       </c>
       <c r="L184" s="7">
-        <f>J184-K184</f>
+        <f t="shared" si="5"/>
         <v>110.09719999999999</v>
       </c>
       <c r="M184" s="4"/>
@@ -8742,11 +8920,11 @@
         <v>60.088000000000001</v>
       </c>
       <c r="J185" s="7">
-        <f>G185*0.94-H185</f>
+        <f t="shared" si="4"/>
         <v>55.581399999999995</v>
       </c>
       <c r="L185" s="7">
-        <f>J185-K185</f>
+        <f t="shared" si="5"/>
         <v>55.581399999999995</v>
       </c>
       <c r="M185" s="4"/>
@@ -8780,14 +8958,14 @@
         <v>9.68</v>
       </c>
       <c r="J186" s="7">
-        <f>G186*0.94-H186</f>
+        <f t="shared" si="4"/>
         <v>8.9539999999999988</v>
       </c>
       <c r="K186" s="7">
         <v>8.9540000000000006</v>
       </c>
       <c r="L186" s="7">
-        <f>J186-K186</f>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="M186" s="4">
@@ -8823,14 +9001,14 @@
         <v>133.42400000000001</v>
       </c>
       <c r="J187" s="7">
-        <f>G187*0.94-H187</f>
+        <f t="shared" si="4"/>
         <v>123.41720000000001</v>
       </c>
       <c r="K187" s="7">
         <v>123.419</v>
       </c>
       <c r="L187" s="7">
-        <f>J187-K187</f>
+        <f t="shared" si="5"/>
         <v>-1.7999999999886995E-3</v>
       </c>
       <c r="M187" s="4">
@@ -8866,14 +9044,14 @@
         <v>23.687999999999999</v>
       </c>
       <c r="J188" s="7">
-        <f>G188*0.94-H188</f>
+        <f t="shared" si="4"/>
         <v>21.911399999999997</v>
       </c>
       <c r="K188" s="7">
         <v>21.911000000000001</v>
       </c>
       <c r="L188" s="7">
-        <f>J188-K188</f>
+        <f t="shared" si="5"/>
         <v>3.9999999999551505E-4</v>
       </c>
       <c r="M188" s="4">
@@ -8909,14 +9087,14 @@
         <v>20.968</v>
       </c>
       <c r="J189" s="7">
-        <f>G189*0.94-H189</f>
+        <f t="shared" si="4"/>
         <v>19.395399999999999</v>
       </c>
       <c r="K189" s="7">
         <v>19.395</v>
       </c>
       <c r="L189" s="7">
-        <f>J189-K189</f>
+        <f t="shared" si="5"/>
         <v>3.9999999999906777E-4</v>
       </c>
       <c r="M189" s="4">
@@ -8952,11 +9130,11 @@
         <v>42.024000000000001</v>
       </c>
       <c r="J190" s="7">
-        <f>G190*0.94-H190</f>
+        <f t="shared" si="4"/>
         <v>38.872199999999999</v>
       </c>
       <c r="L190" s="7">
-        <f>J190-K190</f>
+        <f t="shared" si="5"/>
         <v>38.872199999999999</v>
       </c>
       <c r="M190" s="4"/>
@@ -8990,11 +9168,11 @@
         <v>93.415999999999997</v>
       </c>
       <c r="J191" s="7">
-        <f>G191*0.94-H191</f>
+        <f t="shared" si="4"/>
         <v>86.40979999999999</v>
       </c>
       <c r="L191" s="7">
-        <f>J191-K191</f>
+        <f t="shared" si="5"/>
         <v>86.40979999999999</v>
       </c>
       <c r="M191" s="4"/>
@@ -9028,11 +9206,11 @@
         <v>38.064</v>
       </c>
       <c r="J192" s="7">
-        <f>G192*0.94-H192</f>
+        <f t="shared" si="4"/>
         <v>35.209199999999996</v>
       </c>
       <c r="L192" s="7">
-        <f>J192-K192</f>
+        <f t="shared" si="5"/>
         <v>35.209199999999996</v>
       </c>
       <c r="M192" s="4"/>
@@ -9066,14 +9244,14 @@
         <v>94.512</v>
       </c>
       <c r="J193" s="7">
-        <f>G193*0.94-H193</f>
+        <f t="shared" si="4"/>
         <v>87.423599999999993</v>
       </c>
       <c r="K193" s="7">
         <v>87.426000000000002</v>
       </c>
       <c r="L193" s="7">
-        <f>J193-K193</f>
+        <f t="shared" si="5"/>
         <v>-2.4000000000086175E-3</v>
       </c>
       <c r="M193" s="4">
@@ -9109,14 +9287,14 @@
         <v>35.872</v>
       </c>
       <c r="J194" s="7">
-        <f>G194*0.94-H194</f>
+        <f t="shared" ref="J194:J257" si="6">G194*0.94-H194</f>
         <v>33.181600000000003</v>
       </c>
       <c r="K194" s="7">
         <v>33.182000000000002</v>
       </c>
       <c r="L194" s="7">
-        <f>J194-K194</f>
+        <f t="shared" ref="L194:L257" si="7">J194-K194</f>
         <v>-3.9999999999906777E-4</v>
       </c>
       <c r="M194" s="4">
@@ -9152,14 +9330,14 @@
         <v>15.352</v>
       </c>
       <c r="J195" s="7">
-        <f>G195*0.94-H195</f>
+        <f t="shared" si="6"/>
         <v>14.200599999999998</v>
       </c>
       <c r="K195" s="7">
         <v>14.201000000000001</v>
       </c>
       <c r="L195" s="7">
-        <f>J195-K195</f>
+        <f t="shared" si="7"/>
         <v>-4.0000000000262048E-4</v>
       </c>
       <c r="M195" s="4">
@@ -9195,14 +9373,14 @@
         <v>155.80799999999999</v>
       </c>
       <c r="J196" s="7">
-        <f>G196*0.94-H196</f>
+        <f t="shared" si="6"/>
         <v>144.12239999999997</v>
       </c>
       <c r="K196" s="7">
         <v>144.12299999999999</v>
       </c>
       <c r="L196" s="7">
-        <f>J196-K196</f>
+        <f t="shared" si="7"/>
         <v>-6.0000000001991793E-4</v>
       </c>
       <c r="M196" s="4">
@@ -9238,14 +9416,14 @@
         <v>47.984000000000002</v>
       </c>
       <c r="J197" s="7">
-        <f>G197*0.94-H197</f>
+        <f t="shared" si="6"/>
         <v>44.38519999999999</v>
       </c>
       <c r="K197" s="7">
         <v>44.386000000000003</v>
       </c>
       <c r="L197" s="7">
-        <f>J197-K197</f>
+        <f t="shared" si="7"/>
         <v>-8.0000000001234639E-4</v>
       </c>
       <c r="M197" s="4">
@@ -9281,14 +9459,14 @@
         <v>219.59200000000001</v>
       </c>
       <c r="J198" s="7">
-        <f>G198*0.94-H198</f>
+        <f t="shared" si="6"/>
         <v>203.12260000000001</v>
       </c>
       <c r="K198" s="7">
         <v>203.124</v>
       </c>
       <c r="L198" s="7">
-        <f>J198-K198</f>
+        <f t="shared" si="7"/>
         <v>-1.3999999999896318E-3</v>
       </c>
       <c r="M198" s="4">
@@ -9324,14 +9502,14 @@
         <v>42.264000000000003</v>
       </c>
       <c r="J199" s="7">
-        <f>G199*0.94-H199</f>
+        <f t="shared" si="6"/>
         <v>39.094199999999994</v>
       </c>
       <c r="K199" s="7">
         <v>39.094999999999999</v>
       </c>
       <c r="L199" s="7">
-        <f>J199-K199</f>
+        <f t="shared" si="7"/>
         <v>-8.0000000000524096E-4</v>
       </c>
       <c r="M199" s="4">
@@ -9367,14 +9545,14 @@
         <v>141.54400000000001</v>
       </c>
       <c r="J200" s="7">
-        <f>G200*0.94-H200</f>
+        <f t="shared" si="6"/>
         <v>130.9282</v>
       </c>
       <c r="K200" s="7">
         <v>130.928</v>
       </c>
       <c r="L200" s="7">
-        <f>J200-K200</f>
+        <f t="shared" si="7"/>
         <v>2.0000000000663931E-4</v>
       </c>
       <c r="M200" s="4">
@@ -9410,14 +9588,14 @@
         <v>15.656000000000001</v>
       </c>
       <c r="J201" s="7">
-        <f>G201*0.94-H201</f>
+        <f t="shared" si="6"/>
         <v>14.481799999999998</v>
       </c>
       <c r="K201" s="7">
         <v>14.481999999999999</v>
       </c>
       <c r="L201" s="7">
-        <f>J201-K201</f>
+        <f t="shared" si="7"/>
         <v>-2.0000000000131024E-4</v>
       </c>
       <c r="M201" s="4">
@@ -9453,14 +9631,14 @@
         <v>55</v>
       </c>
       <c r="J202" s="7">
-        <f>G202*0.94-H202</f>
+        <f t="shared" si="6"/>
         <v>50.875</v>
       </c>
       <c r="K202" s="7">
         <v>50.875</v>
       </c>
       <c r="L202" s="7">
-        <f>J202-K202</f>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="M202" s="4">
@@ -9496,14 +9674,14 @@
         <v>23.896000000000001</v>
       </c>
       <c r="J203" s="7">
-        <f>G203*0.94-H203</f>
+        <f t="shared" si="6"/>
         <v>22.1038</v>
       </c>
       <c r="K203" s="7">
         <v>22.103999999999999</v>
       </c>
       <c r="L203" s="7">
-        <f>J203-K203</f>
+        <f t="shared" si="7"/>
         <v>-1.9999999999953388E-4</v>
       </c>
       <c r="M203" s="4">
@@ -9539,14 +9717,14 @@
         <v>30.591999999999999</v>
       </c>
       <c r="J204" s="7">
-        <f>G204*0.94-H204</f>
+        <f t="shared" si="6"/>
         <v>28.297599999999999</v>
       </c>
       <c r="K204" s="7">
         <v>28.297999999999998</v>
       </c>
       <c r="L204" s="7">
-        <f>J204-K204</f>
+        <f t="shared" si="7"/>
         <v>-3.9999999999906777E-4</v>
       </c>
       <c r="M204" s="4">
@@ -9582,11 +9760,11 @@
         <v>81.695999999999998</v>
       </c>
       <c r="J205" s="7">
-        <f>G205*0.94-H205</f>
+        <f t="shared" si="6"/>
         <v>75.56880000000001</v>
       </c>
       <c r="L205" s="7">
-        <f>J205-K205</f>
+        <f t="shared" si="7"/>
         <v>75.56880000000001</v>
       </c>
       <c r="M205" s="4"/>
@@ -9620,11 +9798,11 @@
         <v>132.89599999999999</v>
       </c>
       <c r="J206" s="7">
-        <f>G206*0.94-H206</f>
+        <f t="shared" si="6"/>
         <v>122.9288</v>
       </c>
       <c r="L206" s="7">
-        <f>J206-K206</f>
+        <f t="shared" si="7"/>
         <v>122.9288</v>
       </c>
       <c r="M206" s="4"/>
@@ -9658,11 +9836,11 @@
         <v>58.384</v>
       </c>
       <c r="J207" s="7">
-        <f>G207*0.94-H207</f>
+        <f t="shared" si="6"/>
         <v>54.005200000000002</v>
       </c>
       <c r="L207" s="7">
-        <f>J207-K207</f>
+        <f t="shared" si="7"/>
         <v>54.005200000000002</v>
       </c>
       <c r="M207" s="4"/>
@@ -9696,14 +9874,14 @@
         <v>18.963999999999999</v>
       </c>
       <c r="J208" s="7">
-        <f>G208*0.94-H208</f>
+        <f t="shared" si="6"/>
         <v>17.541699999999999</v>
       </c>
       <c r="K208" s="7">
         <v>17.542000000000002</v>
       </c>
       <c r="L208" s="7">
-        <f>J208-K208</f>
+        <f t="shared" si="7"/>
         <v>-3.0000000000285354E-4</v>
       </c>
       <c r="M208" s="4">
@@ -9739,14 +9917,14 @@
         <v>37.008000000000003</v>
       </c>
       <c r="J209" s="7">
-        <f>G209*0.94-H209</f>
+        <f t="shared" si="6"/>
         <v>34.232399999999991</v>
       </c>
       <c r="K209" s="7">
         <v>34.231999999999999</v>
       </c>
       <c r="L209" s="7">
-        <f>J209-K209</f>
+        <f t="shared" si="7"/>
         <v>3.9999999999196234E-4</v>
       </c>
       <c r="M209" s="4">
@@ -9782,14 +9960,14 @@
         <v>31.99</v>
       </c>
       <c r="J210" s="7">
-        <f>G210*0.94-H210</f>
+        <f t="shared" si="6"/>
         <v>29.590780000000002</v>
       </c>
       <c r="K210" s="7">
         <v>29.591999999999999</v>
       </c>
       <c r="L210" s="7">
-        <f>J210-K210</f>
+        <f t="shared" si="7"/>
         <v>-1.2199999999964461E-3</v>
       </c>
       <c r="M210" s="4">
@@ -9825,11 +10003,11 @@
         <v>41.088000000000001</v>
       </c>
       <c r="J211" s="7">
-        <f>G211*0.94-H211</f>
+        <f t="shared" si="6"/>
         <v>38.006399999999999</v>
       </c>
       <c r="L211" s="7">
-        <f>J211-K211</f>
+        <f t="shared" si="7"/>
         <v>38.006399999999999</v>
       </c>
       <c r="M211" s="4"/>
@@ -9863,11 +10041,11 @@
         <v>15.16</v>
       </c>
       <c r="J212" s="7">
-        <f>G212*0.94-H212</f>
+        <f t="shared" si="6"/>
         <v>14.023</v>
       </c>
       <c r="L212" s="7">
-        <f>J212-K212</f>
+        <f t="shared" si="7"/>
         <v>14.023</v>
       </c>
       <c r="M212" s="4"/>
@@ -9901,11 +10079,11 @@
         <v>64.287999999999997</v>
       </c>
       <c r="J213" s="7">
-        <f>G213*0.94-H213</f>
+        <f t="shared" si="6"/>
         <v>59.466399999999993</v>
       </c>
       <c r="L213" s="7">
-        <f>J213-K213</f>
+        <f t="shared" si="7"/>
         <v>59.466399999999993</v>
       </c>
       <c r="M213" s="4"/>
@@ -9939,11 +10117,11 @@
         <v>14.496</v>
       </c>
       <c r="J214" s="7">
-        <f>G214*0.94-H214</f>
+        <f t="shared" si="6"/>
         <v>13.408800000000001</v>
       </c>
       <c r="L214" s="7">
-        <f>J214-K214</f>
+        <f t="shared" si="7"/>
         <v>13.408800000000001</v>
       </c>
       <c r="M214" s="4"/>
@@ -9977,11 +10155,11 @@
         <v>22.776</v>
       </c>
       <c r="J215" s="7">
-        <f>G215*0.94-H215</f>
+        <f t="shared" si="6"/>
         <v>21.067799999999998</v>
       </c>
       <c r="L215" s="7">
-        <f>J215-K215</f>
+        <f t="shared" si="7"/>
         <v>21.067799999999998</v>
       </c>
       <c r="M215" s="4"/>
@@ -10015,14 +10193,14 @@
         <v>44.128</v>
       </c>
       <c r="J216" s="7">
-        <f>G216*0.94-H216</f>
+        <f t="shared" si="6"/>
         <v>40.818399999999997</v>
       </c>
       <c r="K216" s="7">
         <v>40.817</v>
       </c>
       <c r="L216" s="7">
-        <f>J216-K216</f>
+        <f t="shared" si="7"/>
         <v>1.3999999999967372E-3</v>
       </c>
       <c r="M216" s="4">
@@ -10058,14 +10236,14 @@
         <v>94.512</v>
       </c>
       <c r="J217" s="7">
-        <f>G217*0.94-H217</f>
+        <f t="shared" si="6"/>
         <v>87.423599999999993</v>
       </c>
       <c r="K217" s="7">
         <v>87.426000000000002</v>
       </c>
       <c r="L217" s="7">
-        <f>J217-K217</f>
+        <f t="shared" si="7"/>
         <v>-2.4000000000086175E-3</v>
       </c>
       <c r="M217" s="4">
@@ -10101,14 +10279,14 @@
         <v>35.872</v>
       </c>
       <c r="J218" s="7">
-        <f>G218*0.94-H218</f>
+        <f t="shared" si="6"/>
         <v>33.181600000000003</v>
       </c>
       <c r="K218" s="7">
         <v>33.182000000000002</v>
       </c>
       <c r="L218" s="7">
-        <f>J218-K218</f>
+        <f t="shared" si="7"/>
         <v>-3.9999999999906777E-4</v>
       </c>
       <c r="M218" s="4">
@@ -10144,14 +10322,14 @@
         <v>20.143999999999998</v>
       </c>
       <c r="J219" s="7">
-        <f>G219*0.94-H219</f>
+        <f t="shared" si="6"/>
         <v>18.633200000000002</v>
       </c>
       <c r="K219" s="7">
         <v>18.634</v>
       </c>
       <c r="L219" s="7">
-        <f>J219-K219</f>
+        <f t="shared" si="7"/>
         <v>-7.9999999999813554E-4</v>
       </c>
       <c r="M219" s="4">
@@ -10187,14 +10365,14 @@
         <v>155.80799999999999</v>
       </c>
       <c r="J220" s="7">
-        <f>G220*0.94-H220</f>
+        <f t="shared" si="6"/>
         <v>144.12239999999997</v>
       </c>
       <c r="K220" s="7">
         <v>144.12299999999999</v>
       </c>
       <c r="L220" s="7">
-        <f>J220-K220</f>
+        <f t="shared" si="7"/>
         <v>-6.0000000001991793E-4</v>
       </c>
       <c r="M220" s="4">
@@ -10230,14 +10408,14 @@
         <v>47.984000000000002</v>
       </c>
       <c r="J221" s="7">
-        <f>G221*0.94-H221</f>
+        <f t="shared" si="6"/>
         <v>44.38519999999999</v>
       </c>
       <c r="K221" s="7">
         <v>44.386000000000003</v>
       </c>
       <c r="L221" s="7">
-        <f>J221-K221</f>
+        <f t="shared" si="7"/>
         <v>-8.0000000001234639E-4</v>
       </c>
       <c r="M221" s="4">
@@ -10273,14 +10451,14 @@
         <v>69.176000000000002</v>
       </c>
       <c r="J222" s="7">
-        <f>G222*0.94-H222</f>
+        <f t="shared" si="6"/>
         <v>63.987799999999993</v>
       </c>
       <c r="K222" s="7">
         <v>63.988</v>
       </c>
       <c r="L222" s="7">
-        <f>J222-K222</f>
+        <f t="shared" si="7"/>
         <v>-2.0000000000663931E-4</v>
       </c>
       <c r="M222" s="4">
@@ -10316,14 +10494,14 @@
         <v>154.136</v>
       </c>
       <c r="J223" s="7">
-        <f>G223*0.94-H223</f>
+        <f t="shared" si="6"/>
         <v>142.57579999999999</v>
       </c>
       <c r="K223" s="7">
         <v>142.577</v>
       </c>
       <c r="L223" s="7">
-        <f>J223-K223</f>
+        <f t="shared" si="7"/>
         <v>-1.2000000000114142E-3</v>
       </c>
       <c r="M223" s="4">
@@ -10359,14 +10537,14 @@
         <v>42.264000000000003</v>
       </c>
       <c r="J224" s="7">
-        <f>G224*0.94-H224</f>
+        <f t="shared" si="6"/>
         <v>39.094199999999994</v>
       </c>
       <c r="K224" s="7">
         <v>39.094999999999999</v>
       </c>
       <c r="L224" s="7">
-        <f>J224-K224</f>
+        <f t="shared" si="7"/>
         <v>-8.0000000000524096E-4</v>
       </c>
       <c r="M224" s="4">
@@ -10402,14 +10580,14 @@
         <v>9.68</v>
       </c>
       <c r="J225" s="7">
-        <f>G225*0.94-H225</f>
+        <f t="shared" si="6"/>
         <v>8.9539999999999988</v>
       </c>
       <c r="K225" s="7">
         <v>8.9540000000000006</v>
       </c>
       <c r="L225" s="7">
-        <f>J225-K225</f>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="M225" s="4">
@@ -10445,14 +10623,14 @@
         <v>45.36</v>
       </c>
       <c r="J226" s="7">
-        <f>G226*0.94-H226</f>
+        <f t="shared" si="6"/>
         <v>41.957999999999998</v>
       </c>
       <c r="K226" s="7">
         <v>41.957999999999998</v>
       </c>
       <c r="L226" s="7">
-        <f>J226-K226</f>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="M226" s="4">
@@ -10488,14 +10666,14 @@
         <v>29.224</v>
       </c>
       <c r="J227" s="7">
-        <f>G227*0.94-H227</f>
+        <f t="shared" si="6"/>
         <v>27.0322</v>
       </c>
       <c r="K227" s="7">
         <v>27.032</v>
       </c>
       <c r="L227" s="7">
-        <f>J227-K227</f>
+        <f t="shared" si="7"/>
         <v>1.9999999999953388E-4</v>
       </c>
       <c r="M227" s="4">
@@ -10531,11 +10709,11 @@
         <v>74.048000000000002</v>
       </c>
       <c r="J228" s="7">
-        <f>G228*0.94-H228</f>
+        <f t="shared" si="6"/>
         <v>68.494399999999999</v>
       </c>
       <c r="L228" s="7">
-        <f>J228-K228</f>
+        <f t="shared" si="7"/>
         <v>68.494399999999999</v>
       </c>
       <c r="M228" s="4"/>
@@ -10569,14 +10747,14 @@
         <v>23.896000000000001</v>
       </c>
       <c r="J229" s="7">
-        <f>G229*0.94-H229</f>
+        <f t="shared" si="6"/>
         <v>22.1038</v>
       </c>
       <c r="K229" s="7">
         <v>22.103999999999999</v>
       </c>
       <c r="L229" s="7">
-        <f>J229-K229</f>
+        <f t="shared" si="7"/>
         <v>-1.9999999999953388E-4</v>
       </c>
       <c r="M229" s="4">
@@ -10612,11 +10790,11 @@
         <v>130.44</v>
       </c>
       <c r="J230" s="7">
-        <f>G230*0.94-H230</f>
+        <f t="shared" si="6"/>
         <v>120.657</v>
       </c>
       <c r="L230" s="7">
-        <f>J230-K230</f>
+        <f t="shared" si="7"/>
         <v>120.657</v>
       </c>
       <c r="M230" s="4"/>
@@ -10650,11 +10828,11 @@
         <v>39.408000000000001</v>
       </c>
       <c r="J231" s="7">
-        <f>G231*0.94-H231</f>
+        <f t="shared" si="6"/>
         <v>36.452399999999997</v>
       </c>
       <c r="L231" s="7">
-        <f>J231-K231</f>
+        <f t="shared" si="7"/>
         <v>36.452399999999997</v>
       </c>
       <c r="M231" s="4"/>
@@ -10688,14 +10866,14 @@
         <v>193.64</v>
       </c>
       <c r="J232" s="7">
-        <f>G232*0.94-H232</f>
+        <f t="shared" si="6"/>
         <v>179.11699999999999</v>
       </c>
       <c r="K232" s="7">
         <v>179.11699999999999</v>
       </c>
       <c r="L232" s="7">
-        <f>J232-K232</f>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="M232" s="4">
@@ -10731,14 +10909,14 @@
         <v>38.088000000000001</v>
       </c>
       <c r="J233" s="7">
-        <f>G233*0.94-H233</f>
+        <f t="shared" si="6"/>
         <v>35.231400000000001</v>
       </c>
       <c r="K233" s="7">
         <v>35.229999999999997</v>
       </c>
       <c r="L233" s="7">
-        <f>J233-K233</f>
+        <f t="shared" si="7"/>
         <v>1.4000000000038426E-3</v>
       </c>
       <c r="M233" s="4">
@@ -10774,11 +10952,11 @@
         <v>23</v>
       </c>
       <c r="J234" s="7">
-        <f>G234*0.94-H234</f>
+        <f t="shared" si="6"/>
         <v>21.274999999999999</v>
       </c>
       <c r="L234" s="7">
-        <f>J234-K234</f>
+        <f t="shared" si="7"/>
         <v>21.274999999999999</v>
       </c>
       <c r="M234" s="4"/>
@@ -10812,11 +10990,11 @@
         <v>78.024000000000001</v>
       </c>
       <c r="J235" s="7">
-        <f>G235*0.94-H235</f>
+        <f t="shared" si="6"/>
         <v>72.172199999999989</v>
       </c>
       <c r="L235" s="7">
-        <f>J235-K235</f>
+        <f t="shared" si="7"/>
         <v>72.172199999999989</v>
       </c>
       <c r="M235" s="4"/>
@@ -10850,11 +11028,11 @@
         <v>94.512</v>
       </c>
       <c r="J236" s="7">
-        <f>G236*0.94-H236</f>
+        <f t="shared" si="6"/>
         <v>87.423599999999993</v>
       </c>
       <c r="L236" s="7">
-        <f>J236-K236</f>
+        <f t="shared" si="7"/>
         <v>87.423599999999993</v>
       </c>
       <c r="M236" s="4"/>
@@ -10888,11 +11066,11 @@
         <v>35.872</v>
       </c>
       <c r="J237" s="7">
-        <f>G237*0.94-H237</f>
+        <f t="shared" si="6"/>
         <v>33.181600000000003</v>
       </c>
       <c r="L237" s="7">
-        <f>J237-K237</f>
+        <f t="shared" si="7"/>
         <v>33.181600000000003</v>
       </c>
       <c r="M237" s="4"/>
@@ -10926,11 +11104,11 @@
         <v>15.352</v>
       </c>
       <c r="J238" s="7">
-        <f>G238*0.94-H238</f>
+        <f t="shared" si="6"/>
         <v>14.200599999999998</v>
       </c>
       <c r="L238" s="7">
-        <f>J238-K238</f>
+        <f t="shared" si="7"/>
         <v>14.200599999999998</v>
       </c>
       <c r="M238" s="4"/>
@@ -10964,11 +11142,11 @@
         <v>146.608</v>
       </c>
       <c r="J239" s="7">
-        <f>G239*0.94-H239</f>
+        <f t="shared" si="6"/>
         <v>135.61239999999998</v>
       </c>
       <c r="L239" s="7">
-        <f>J239-K239</f>
+        <f t="shared" si="7"/>
         <v>135.61239999999998</v>
       </c>
       <c r="M239" s="4"/>
@@ -11002,11 +11180,11 @@
         <v>47.984000000000002</v>
       </c>
       <c r="J240" s="7">
-        <f>G240*0.94-H240</f>
+        <f t="shared" si="6"/>
         <v>44.38519999999999</v>
       </c>
       <c r="L240" s="7">
-        <f>J240-K240</f>
+        <f t="shared" si="7"/>
         <v>44.38519999999999</v>
       </c>
       <c r="M240" s="4"/>
@@ -11040,11 +11218,11 @@
         <v>95.111999999999995</v>
       </c>
       <c r="J241" s="7">
-        <f>G241*0.94-H241</f>
+        <f t="shared" si="6"/>
         <v>87.9786</v>
       </c>
       <c r="L241" s="7">
-        <f>J241-K241</f>
+        <f t="shared" si="7"/>
         <v>87.9786</v>
       </c>
       <c r="M241" s="4"/>
@@ -11078,11 +11256,11 @@
         <v>154.136</v>
       </c>
       <c r="J242" s="7">
-        <f>G242*0.94-H242</f>
+        <f t="shared" si="6"/>
         <v>142.57579999999999</v>
       </c>
       <c r="L242" s="7">
-        <f>J242-K242</f>
+        <f t="shared" si="7"/>
         <v>142.57579999999999</v>
       </c>
       <c r="M242" s="4"/>
@@ -11116,11 +11294,11 @@
         <v>133.42400000000001</v>
       </c>
       <c r="J243" s="7">
-        <f>G243*0.94-H243</f>
+        <f t="shared" si="6"/>
         <v>123.41720000000001</v>
       </c>
       <c r="L243" s="7">
-        <f>J243-K243</f>
+        <f t="shared" si="7"/>
         <v>123.41720000000001</v>
       </c>
       <c r="M243" s="4"/>
@@ -11154,11 +11332,11 @@
         <v>42.264000000000003</v>
       </c>
       <c r="J244" s="7">
-        <f>G244*0.94-H244</f>
+        <f t="shared" si="6"/>
         <v>39.094199999999994</v>
       </c>
       <c r="L244" s="7">
-        <f>J244-K244</f>
+        <f t="shared" si="7"/>
         <v>39.094199999999994</v>
       </c>
       <c r="M244" s="4"/>
@@ -11192,11 +11370,11 @@
         <v>9.68</v>
       </c>
       <c r="J245" s="7">
-        <f>G245*0.94-H245</f>
+        <f t="shared" si="6"/>
         <v>8.9539999999999988</v>
       </c>
       <c r="L245" s="7">
-        <f>J245-K245</f>
+        <f t="shared" si="7"/>
         <v>8.9539999999999988</v>
       </c>
       <c r="M245" s="4"/>
@@ -11230,11 +11408,11 @@
         <v>50.415999999999997</v>
       </c>
       <c r="J246" s="7">
-        <f>G246*0.94-H246</f>
+        <f t="shared" si="6"/>
         <v>46.634799999999998</v>
       </c>
       <c r="L246" s="7">
-        <f>J246-K246</f>
+        <f t="shared" si="7"/>
         <v>46.634799999999998</v>
       </c>
       <c r="M246" s="4"/>
@@ -11268,11 +11446,11 @@
         <v>54.368000000000002</v>
       </c>
       <c r="J247" s="7">
-        <f>G247*0.94-H247</f>
+        <f t="shared" si="6"/>
         <v>50.290399999999991</v>
       </c>
       <c r="L247" s="7">
-        <f>J247-K247</f>
+        <f t="shared" si="7"/>
         <v>50.290399999999991</v>
       </c>
       <c r="M247" s="4"/>
@@ -11306,11 +11484,11 @@
         <v>19.391999999999999</v>
       </c>
       <c r="J248" s="7">
-        <f>G248*0.94-H248</f>
+        <f t="shared" si="6"/>
         <v>17.9376</v>
       </c>
       <c r="L248" s="7">
-        <f>J248-K248</f>
+        <f t="shared" si="7"/>
         <v>17.9376</v>
       </c>
       <c r="M248" s="4"/>
@@ -11344,11 +11522,11 @@
         <v>23.896000000000001</v>
       </c>
       <c r="J249" s="7">
-        <f>G249*0.94-H249</f>
+        <f t="shared" si="6"/>
         <v>22.1038</v>
       </c>
       <c r="L249" s="7">
-        <f>J249-K249</f>
+        <f t="shared" si="7"/>
         <v>22.1038</v>
       </c>
       <c r="M249" s="4"/>
@@ -11382,11 +11560,11 @@
         <v>29.224</v>
       </c>
       <c r="J250" s="7">
-        <f>G250*0.94-H250</f>
+        <f t="shared" si="6"/>
         <v>27.0322</v>
       </c>
       <c r="L250" s="7">
-        <f>J250-K250</f>
+        <f t="shared" si="7"/>
         <v>27.0322</v>
       </c>
       <c r="M250" s="4"/>
@@ -11420,11 +11598,11 @@
         <v>77.207999999999998</v>
       </c>
       <c r="J251" s="7">
-        <f>G251*0.94-H251</f>
+        <f t="shared" si="6"/>
         <v>71.417399999999986</v>
       </c>
       <c r="L251" s="7">
-        <f>J251-K251</f>
+        <f t="shared" si="7"/>
         <v>71.417399999999986</v>
       </c>
       <c r="M251" s="4"/>
@@ -11458,11 +11636,11 @@
         <v>39.408000000000001</v>
       </c>
       <c r="J252" s="7">
-        <f>G252*0.94-H252</f>
+        <f t="shared" si="6"/>
         <v>36.452399999999997</v>
       </c>
       <c r="L252" s="7">
-        <f>J252-K252</f>
+        <f t="shared" si="7"/>
         <v>36.452399999999997</v>
       </c>
       <c r="M252" s="4"/>
@@ -11496,11 +11674,11 @@
         <v>99.751999999999995</v>
       </c>
       <c r="J253" s="7">
-        <f>G253*0.94-H253</f>
+        <f t="shared" si="6"/>
         <v>92.270599999999988</v>
       </c>
       <c r="L253" s="7">
-        <f>J253-K253</f>
+        <f t="shared" si="7"/>
         <v>92.270599999999988</v>
       </c>
       <c r="M253" s="4"/>
@@ -11534,11 +11712,11 @@
         <v>6.4880000000000004</v>
       </c>
       <c r="J254" s="7">
-        <f>G254*0.94-H254</f>
+        <f t="shared" si="6"/>
         <v>6.0013999999999994</v>
       </c>
       <c r="L254" s="7">
-        <f>J254-K254</f>
+        <f t="shared" si="7"/>
         <v>6.0013999999999994</v>
       </c>
       <c r="M254" s="4"/>
@@ -11572,11 +11750,11 @@
         <v>52.472000000000001</v>
       </c>
       <c r="J255" s="7">
-        <f>G255*0.94-H255</f>
+        <f t="shared" si="6"/>
         <v>48.5366</v>
       </c>
       <c r="L255" s="7">
-        <f>J255-K255</f>
+        <f t="shared" si="7"/>
         <v>48.5366</v>
       </c>
       <c r="M255" s="4"/>
@@ -11610,11 +11788,11 @@
         <v>23.952000000000002</v>
       </c>
       <c r="J256" s="7">
-        <f>G256*0.94-H256</f>
+        <f t="shared" si="6"/>
         <v>22.1556</v>
       </c>
       <c r="L256" s="7">
-        <f>J256-K256</f>
+        <f t="shared" si="7"/>
         <v>22.1556</v>
       </c>
       <c r="M256" s="4"/>
@@ -11648,14 +11826,30 @@
         <v>24.768000000000001</v>
       </c>
       <c r="J257" s="7">
-        <f>G257*0.94-H257</f>
+        <f t="shared" si="6"/>
         <v>22.910399999999999</v>
       </c>
       <c r="L257" s="7">
-        <f>J257-K257</f>
+        <f t="shared" si="7"/>
         <v>22.910399999999999</v>
       </c>
       <c r="M257" s="4"/>
+    </row>
+    <row r="258" spans="1:13" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A258" s="2"/>
+      <c r="B258" s="2"/>
+      <c r="C258" s="2"/>
+      <c r="D258" s="2"/>
+      <c r="E258" s="2"/>
+      <c r="F258" s="3"/>
+      <c r="G258" s="6"/>
+      <c r="H258" s="6"/>
+      <c r="I258" s="6"/>
+      <c r="K258" s="7">
+        <f>SUBTOTAL(109,Table1[المدفوع])</f>
+        <v>10730.002999999997</v>
+      </c>
+      <c r="M258" s="4"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
